--- a/research/traditional_assets/database/data/slovenia/slovenia_power.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_power.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07222119884477141</v>
+        <v>0.07212042856696635</v>
       </c>
       <c r="C2">
-        <v>126.2979072777337</v>
+        <v>125.1324012332792</v>
       </c>
       <c r="D2">
-        <v>126.0999072777337</v>
+        <v>126.1764012332792</v>
       </c>
       <c r="E2">
-        <v>-62.2</v>
+        <v>-60.95800000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.242</v>
       </c>
       <c r="G2">
         <v>0.198</v>
@@ -1433,28 +1433,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0624726</v>
       </c>
       <c r="N2">
-        <v>9.449999999999999</v>
+        <v>9.3875274</v>
       </c>
       <c r="O2">
-        <v>1.7955</v>
+        <v>1.783630206</v>
       </c>
       <c r="P2">
-        <v>7.6545</v>
+        <v>7.603897194</v>
       </c>
       <c r="Q2">
-        <v>27.9545</v>
+        <v>27.903897194</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07222119884477141</v>
+        <v>0.07243737228986499</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.4491443646317593</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>151.2663151525629</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07212042856696635</v>
+        <v>0.07201965828916128</v>
       </c>
       <c r="C3">
-        <v>125.1324012332792</v>
+        <v>123.9669880497476</v>
       </c>
       <c r="D3">
-        <v>126.1764012332792</v>
+        <v>126.2529880497476</v>
       </c>
       <c r="E3">
-        <v>-60.95800000000001</v>
+        <v>-59.716</v>
       </c>
       <c r="F3">
-        <v>1.242</v>
+        <v>2.484</v>
       </c>
       <c r="G3">
         <v>0.198</v>
@@ -1515,28 +1515,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M3">
-        <v>0.0624726</v>
+        <v>0.1249452</v>
       </c>
       <c r="N3">
-        <v>9.3875274</v>
+        <v>9.325054799999998</v>
       </c>
       <c r="O3">
-        <v>1.783630206</v>
+        <v>1.771760412</v>
       </c>
       <c r="P3">
-        <v>7.603897194</v>
+        <v>7.553294387999999</v>
       </c>
       <c r="Q3">
-        <v>27.903897194</v>
+        <v>27.853294388</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07243737228986499</v>
+        <v>0.07265795743791967</v>
       </c>
       <c r="T3">
-        <v>0.4491443646317593</v>
+        <v>0.4528637471253514</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>151.2663151525629</v>
+        <v>75.63315757628143</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07201965828916128</v>
+        <v>0.07191888801135621</v>
       </c>
       <c r="C4">
-        <v>123.9669880497476</v>
+        <v>122.8016678963363</v>
       </c>
       <c r="D4">
-        <v>126.2529880497476</v>
+        <v>126.3296678963363</v>
       </c>
       <c r="E4">
-        <v>-59.716</v>
+        <v>-58.474</v>
       </c>
       <c r="F4">
-        <v>2.484</v>
+        <v>3.726</v>
       </c>
       <c r="G4">
         <v>0.198</v>
@@ -1597,28 +1597,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M4">
-        <v>0.1249452</v>
+        <v>0.1874178</v>
       </c>
       <c r="N4">
-        <v>9.325054799999998</v>
+        <v>9.262582199999999</v>
       </c>
       <c r="O4">
-        <v>1.771760412</v>
+        <v>1.759890618</v>
       </c>
       <c r="P4">
-        <v>7.553294387999999</v>
+        <v>7.502691581999999</v>
       </c>
       <c r="Q4">
-        <v>27.853294388</v>
+        <v>27.802691582</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07265795743791967</v>
+        <v>0.07288309073335691</v>
       </c>
       <c r="T4">
-        <v>0.4528637471253514</v>
+        <v>0.4566598179177805</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.63315757628143</v>
+        <v>50.42210505085429</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07191888801135621</v>
+        <v>0.07181811773355112</v>
       </c>
       <c r="C5">
-        <v>122.8016678963363</v>
+        <v>121.6364409426541</v>
       </c>
       <c r="D5">
-        <v>126.3296678963363</v>
+        <v>126.4064409426542</v>
       </c>
       <c r="E5">
-        <v>-58.474</v>
+        <v>-57.232</v>
       </c>
       <c r="F5">
-        <v>3.726</v>
+        <v>4.968</v>
       </c>
       <c r="G5">
         <v>0.198</v>
@@ -1679,28 +1679,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M5">
-        <v>0.1874178</v>
+        <v>0.2498904</v>
       </c>
       <c r="N5">
-        <v>9.262582199999999</v>
+        <v>9.200109599999999</v>
       </c>
       <c r="O5">
-        <v>1.759890618</v>
+        <v>1.748020824</v>
       </c>
       <c r="P5">
-        <v>7.502691581999999</v>
+        <v>7.452088775999999</v>
       </c>
       <c r="Q5">
-        <v>27.802691582</v>
+        <v>27.752088776</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07288309073335691</v>
+        <v>0.07311291430578243</v>
       </c>
       <c r="T5">
-        <v>0.4566598179177805</v>
+        <v>0.4605349735183852</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.42210505085429</v>
+        <v>37.81657878814072</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07181811773355112</v>
+        <v>0.07171734745574607</v>
       </c>
       <c r="C6">
-        <v>121.6364409426541</v>
+        <v>120.4713073587224</v>
       </c>
       <c r="D6">
-        <v>126.4064409426542</v>
+        <v>126.4833073587224</v>
       </c>
       <c r="E6">
-        <v>-57.232</v>
+        <v>-55.99</v>
       </c>
       <c r="F6">
-        <v>4.968</v>
+        <v>6.210000000000001</v>
       </c>
       <c r="G6">
         <v>0.198</v>
@@ -1761,28 +1761,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M6">
-        <v>0.2498904</v>
+        <v>0.312363</v>
       </c>
       <c r="N6">
-        <v>9.200109599999999</v>
+        <v>9.137637</v>
       </c>
       <c r="O6">
-        <v>1.748020824</v>
+        <v>1.73615103</v>
       </c>
       <c r="P6">
-        <v>7.452088775999999</v>
+        <v>7.40148597</v>
       </c>
       <c r="Q6">
-        <v>27.752088776</v>
+        <v>27.70148597</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07311291430578243</v>
+        <v>0.07334757626920639</v>
       </c>
       <c r="T6">
-        <v>0.4605349735183852</v>
+        <v>0.4644917113421605</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.81657878814072</v>
+        <v>30.25326303051257</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07171734745574607</v>
+        <v>0.07161657717794101</v>
       </c>
       <c r="C7">
-        <v>120.4713073587224</v>
+        <v>119.3062673149762</v>
       </c>
       <c r="D7">
-        <v>126.4833073587224</v>
+        <v>126.5602673149762</v>
       </c>
       <c r="E7">
-        <v>-55.99</v>
+        <v>-54.748</v>
       </c>
       <c r="F7">
-        <v>6.210000000000001</v>
+        <v>7.452000000000001</v>
       </c>
       <c r="G7">
         <v>0.198</v>
@@ -1843,28 +1843,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M7">
-        <v>0.312363</v>
+        <v>0.3748356</v>
       </c>
       <c r="N7">
-        <v>9.137637</v>
+        <v>9.075164399999998</v>
       </c>
       <c r="O7">
-        <v>1.73615103</v>
+        <v>1.724281236</v>
       </c>
       <c r="P7">
-        <v>7.40148597</v>
+        <v>7.350883163999999</v>
       </c>
       <c r="Q7">
-        <v>27.70148597</v>
+        <v>27.650883164</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07334757626920639</v>
+        <v>0.07358723104036277</v>
       </c>
       <c r="T7">
-        <v>0.4644917113421605</v>
+        <v>0.46853263507708</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.25326303051257</v>
+        <v>25.21105252542714</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07161657717794101</v>
+        <v>0.07151580690013595</v>
       </c>
       <c r="C8">
-        <v>119.3062673149762</v>
+        <v>118.1413209822657</v>
       </c>
       <c r="D8">
-        <v>126.5602673149762</v>
+        <v>126.6373209822657</v>
       </c>
       <c r="E8">
-        <v>-54.748</v>
+        <v>-53.506</v>
       </c>
       <c r="F8">
-        <v>7.452</v>
+        <v>8.693999999999999</v>
       </c>
       <c r="G8">
         <v>0.198</v>
@@ -1925,28 +1925,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M8">
-        <v>0.3748356</v>
+        <v>0.4373081999999999</v>
       </c>
       <c r="N8">
-        <v>9.075164399999998</v>
+        <v>9.012691799999999</v>
       </c>
       <c r="O8">
-        <v>1.724281236</v>
+        <v>1.712411442</v>
       </c>
       <c r="P8">
-        <v>7.350883163999999</v>
+        <v>7.300280357999999</v>
       </c>
       <c r="Q8">
-        <v>27.650883164</v>
+        <v>27.600280358</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07358723104036277</v>
+        <v>0.07383203967756553</v>
       </c>
       <c r="T8">
-        <v>0.46853263507708</v>
+        <v>0.4726604603976968</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.21105252542714</v>
+        <v>21.60947359322327</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07151580690013594</v>
+        <v>0.07141503662233088</v>
       </c>
       <c r="C9">
-        <v>118.1413209822657</v>
+        <v>116.9764685318574</v>
       </c>
       <c r="D9">
-        <v>126.6373209822657</v>
+        <v>126.7144685318574</v>
       </c>
       <c r="E9">
-        <v>-53.506</v>
+        <v>-52.264</v>
       </c>
       <c r="F9">
-        <v>8.694000000000001</v>
+        <v>9.936</v>
       </c>
       <c r="G9">
         <v>0.198</v>
@@ -2007,28 +2007,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M9">
-        <v>0.4373082</v>
+        <v>0.4997808</v>
       </c>
       <c r="N9">
-        <v>9.012691799999999</v>
+        <v>8.950219199999999</v>
       </c>
       <c r="O9">
-        <v>1.712411442</v>
+        <v>1.700541648</v>
       </c>
       <c r="P9">
-        <v>7.300280357999999</v>
+        <v>7.249677552</v>
       </c>
       <c r="Q9">
-        <v>27.600280358</v>
+        <v>27.549677552</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07383203967756553</v>
+        <v>0.074082170241664</v>
       </c>
       <c r="T9">
-        <v>0.4726604603976968</v>
+        <v>0.4768780210513703</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.60947359322326</v>
+        <v>18.90828939407036</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07141503662233088</v>
+        <v>0.07131426634452581</v>
       </c>
       <c r="C10">
-        <v>116.9764685318574</v>
+        <v>115.8117101354353</v>
       </c>
       <c r="D10">
-        <v>126.7144685318574</v>
+        <v>126.7917101354354</v>
       </c>
       <c r="E10">
-        <v>-52.264</v>
+        <v>-51.02200000000001</v>
       </c>
       <c r="F10">
-        <v>9.936</v>
+        <v>11.178</v>
       </c>
       <c r="G10">
         <v>0.198</v>
@@ -2089,28 +2089,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M10">
-        <v>0.4997808</v>
+        <v>0.5622533999999999</v>
       </c>
       <c r="N10">
-        <v>8.950219199999999</v>
+        <v>8.8877466</v>
       </c>
       <c r="O10">
-        <v>1.700541648</v>
+        <v>1.688671854</v>
       </c>
       <c r="P10">
-        <v>7.249677552</v>
+        <v>7.199074746</v>
       </c>
       <c r="Q10">
-        <v>27.549677552</v>
+        <v>27.499074746</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.074082170241664</v>
+        <v>0.0743377981807976</v>
       </c>
       <c r="T10">
-        <v>0.4768780210513703</v>
+        <v>0.481188275345784</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.90828939407036</v>
+        <v>16.80736835028477</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07131426634452581</v>
+        <v>0.07121349606672076</v>
       </c>
       <c r="C11">
-        <v>115.8117101354353</v>
+        <v>114.6470459651025</v>
       </c>
       <c r="D11">
-        <v>126.7917101354354</v>
+        <v>126.8690459651025</v>
       </c>
       <c r="E11">
-        <v>-51.02200000000001</v>
+        <v>-49.78</v>
       </c>
       <c r="F11">
-        <v>11.178</v>
+        <v>12.42</v>
       </c>
       <c r="G11">
         <v>0.198</v>
@@ -2171,28 +2171,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M11">
-        <v>0.5622533999999999</v>
+        <v>0.624726</v>
       </c>
       <c r="N11">
-        <v>8.8877466</v>
+        <v>8.825273999999999</v>
       </c>
       <c r="O11">
-        <v>1.688671854</v>
+        <v>1.67680206</v>
       </c>
       <c r="P11">
-        <v>7.199074746</v>
+        <v>7.148471939999999</v>
       </c>
       <c r="Q11">
-        <v>27.499074746</v>
+        <v>27.44847194</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0743377981807976</v>
+        <v>0.07459910674080084</v>
       </c>
       <c r="T11">
-        <v>0.481188275345784</v>
+        <v>0.4855943130689624</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.80736835028477</v>
+        <v>15.12663151525629</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07121349606672076</v>
+        <v>0.07111272578891568</v>
       </c>
       <c r="C12">
-        <v>114.6470459651025</v>
+        <v>113.4824761933821</v>
       </c>
       <c r="D12">
-        <v>126.8690459651025</v>
+        <v>126.9464761933822</v>
       </c>
       <c r="E12">
-        <v>-49.78</v>
+        <v>-48.538</v>
       </c>
       <c r="F12">
-        <v>12.42</v>
+        <v>13.662</v>
       </c>
       <c r="G12">
         <v>0.198</v>
@@ -2253,28 +2253,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M12">
-        <v>0.624726</v>
+        <v>0.6871986</v>
       </c>
       <c r="N12">
-        <v>8.825273999999999</v>
+        <v>8.762801399999999</v>
       </c>
       <c r="O12">
-        <v>1.67680206</v>
+        <v>1.664932266</v>
       </c>
       <c r="P12">
-        <v>7.148471939999999</v>
+        <v>7.097869133999999</v>
       </c>
       <c r="Q12">
-        <v>27.44847194</v>
+        <v>27.397869134</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07459910674080084</v>
+        <v>0.07486628740327604</v>
       </c>
       <c r="T12">
-        <v>0.4855943130689624</v>
+        <v>0.4900993628758077</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.12663151525629</v>
+        <v>13.75148319568753</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07111272578891568</v>
+        <v>0.07115775551111062</v>
       </c>
       <c r="C13">
-        <v>113.4824761933821</v>
+        <v>112.2058644160082</v>
       </c>
       <c r="D13">
-        <v>126.9464761933822</v>
+        <v>126.9118644160082</v>
       </c>
       <c r="E13">
-        <v>-48.538</v>
+        <v>-47.29600000000001</v>
       </c>
       <c r="F13">
-        <v>13.662</v>
+        <v>14.904</v>
       </c>
       <c r="G13">
         <v>0.198</v>
@@ -2335,45 +2335,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M13">
-        <v>0.6871986</v>
+        <v>0.7720272</v>
       </c>
       <c r="N13">
-        <v>8.762801399999999</v>
+        <v>8.677972799999999</v>
       </c>
       <c r="O13">
-        <v>1.664932266</v>
+        <v>1.648814832</v>
       </c>
       <c r="P13">
-        <v>7.097869133999999</v>
+        <v>7.029157968</v>
       </c>
       <c r="Q13">
-        <v>27.397869134</v>
+        <v>27.329157968</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07486628740327604</v>
+        <v>0.07513954035353479</v>
       </c>
       <c r="T13">
-        <v>0.4900993628758077</v>
+        <v>0.4947068001782631</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.19</v>
       </c>
       <c r="W13">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.75148319568753</v>
+        <v>12.24050137093615</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07115775551111062</v>
+        <v>0.07106913523330555</v>
       </c>
       <c r="C14">
-        <v>112.2058644160082</v>
+        <v>111.0319997537231</v>
       </c>
       <c r="D14">
-        <v>126.9118644160082</v>
+        <v>126.9799997537231</v>
       </c>
       <c r="E14">
-        <v>-47.29600000000001</v>
+        <v>-46.054</v>
       </c>
       <c r="F14">
-        <v>14.904</v>
+        <v>16.146</v>
       </c>
       <c r="G14">
         <v>0.198</v>
@@ -2417,28 +2417,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M14">
-        <v>0.7720272</v>
+        <v>0.8363628000000001</v>
       </c>
       <c r="N14">
-        <v>8.677972799999999</v>
+        <v>8.613637199999999</v>
       </c>
       <c r="O14">
-        <v>1.648814832</v>
+        <v>1.636591068</v>
       </c>
       <c r="P14">
-        <v>7.029157968</v>
+        <v>6.977046132</v>
       </c>
       <c r="Q14">
-        <v>27.329157968</v>
+        <v>27.277046132</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07513954035353479</v>
+        <v>0.07541907498081098</v>
       </c>
       <c r="T14">
-        <v>0.4947068001782631</v>
+        <v>0.4994201555796257</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.24050137093615</v>
+        <v>11.2989243424026</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07106913523330555</v>
+        <v>0.07098051495550048</v>
       </c>
       <c r="C15">
-        <v>111.0319997537231</v>
+        <v>109.8582082905511</v>
       </c>
       <c r="D15">
-        <v>126.9799997537231</v>
+        <v>127.0482082905511</v>
       </c>
       <c r="E15">
-        <v>-46.054</v>
+        <v>-44.812</v>
       </c>
       <c r="F15">
-        <v>16.146</v>
+        <v>17.388</v>
       </c>
       <c r="G15">
         <v>0.198</v>
@@ -2499,28 +2499,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M15">
-        <v>0.8363628000000001</v>
+        <v>0.9006984000000001</v>
       </c>
       <c r="N15">
-        <v>8.613637199999999</v>
+        <v>8.5493016</v>
       </c>
       <c r="O15">
-        <v>1.636591068</v>
+        <v>1.624367304</v>
       </c>
       <c r="P15">
-        <v>6.977046132</v>
+        <v>6.924934296</v>
       </c>
       <c r="Q15">
-        <v>27.277046132</v>
+        <v>27.224934296</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07541907498081098</v>
+        <v>0.07570511041337266</v>
       </c>
       <c r="T15">
-        <v>0.4994201555796257</v>
+        <v>0.504243123897299</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.2989243424026</v>
+        <v>10.49185831794527</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07098051495550048</v>
+        <v>0.07109844467769541</v>
       </c>
       <c r="C16">
-        <v>109.8582082905511</v>
+        <v>108.5254572119699</v>
       </c>
       <c r="D16">
-        <v>127.0482082905511</v>
+        <v>126.9574572119699</v>
       </c>
       <c r="E16">
-        <v>-44.812</v>
+        <v>-43.57</v>
       </c>
       <c r="F16">
-        <v>17.388</v>
+        <v>18.63</v>
       </c>
       <c r="G16">
         <v>0.198</v>
@@ -2581,45 +2581,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M16">
-        <v>0.9006984000000001</v>
+        <v>0.9967050000000001</v>
       </c>
       <c r="N16">
-        <v>8.5493016</v>
+        <v>8.453294999999999</v>
       </c>
       <c r="O16">
-        <v>1.624367304</v>
+        <v>1.60612605</v>
       </c>
       <c r="P16">
-        <v>6.924934296</v>
+        <v>6.847168949999999</v>
       </c>
       <c r="Q16">
-        <v>27.224934296</v>
+        <v>27.14716895</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07570511041337266</v>
+        <v>0.07599787609140637</v>
       </c>
       <c r="T16">
-        <v>0.504243123897299</v>
+        <v>0.5091795738224468</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.19</v>
       </c>
       <c r="W16">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.49185831794527</v>
+        <v>9.48124068806718</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07109844467769541</v>
+        <v>0.07102359439989035</v>
       </c>
       <c r="C17">
-        <v>108.5254572119699</v>
+        <v>107.3410421028466</v>
       </c>
       <c r="D17">
-        <v>126.9574572119699</v>
+        <v>127.0150421028466</v>
       </c>
       <c r="E17">
-        <v>-43.57000000000001</v>
+        <v>-42.328</v>
       </c>
       <c r="F17">
-        <v>18.63</v>
+        <v>19.872</v>
       </c>
       <c r="G17">
         <v>0.198</v>
@@ -2663,28 +2663,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M17">
-        <v>0.996705</v>
+        <v>1.063152</v>
       </c>
       <c r="N17">
-        <v>8.453294999999999</v>
+        <v>8.386847999999999</v>
       </c>
       <c r="O17">
-        <v>1.60612605</v>
+        <v>1.59350112</v>
       </c>
       <c r="P17">
-        <v>6.847168949999999</v>
+        <v>6.793346879999999</v>
       </c>
       <c r="Q17">
-        <v>27.14716895</v>
+        <v>27.09334688</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07599787609140637</v>
+        <v>0.07629761238082185</v>
       </c>
       <c r="T17">
-        <v>0.5091795738224468</v>
+        <v>0.514233558269622</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.48124068806718</v>
+        <v>8.888663145062981</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07102359439989035</v>
+        <v>0.07094874412208528</v>
       </c>
       <c r="C18">
-        <v>107.3410421028466</v>
+        <v>106.156679255709</v>
       </c>
       <c r="D18">
-        <v>127.0150421028466</v>
+        <v>127.072679255709</v>
       </c>
       <c r="E18">
-        <v>-42.328</v>
+        <v>-41.086</v>
       </c>
       <c r="F18">
-        <v>19.872</v>
+        <v>21.114</v>
       </c>
       <c r="G18">
         <v>0.198</v>
@@ -2745,28 +2745,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M18">
-        <v>1.063152</v>
+        <v>1.129599</v>
       </c>
       <c r="N18">
-        <v>8.386847999999999</v>
+        <v>8.320400999999999</v>
       </c>
       <c r="O18">
-        <v>1.59350112</v>
+        <v>1.58087619</v>
       </c>
       <c r="P18">
-        <v>6.793346879999999</v>
+        <v>6.739524809999999</v>
       </c>
       <c r="Q18">
-        <v>27.09334688</v>
+        <v>27.03952481</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07629761238082185</v>
+        <v>0.07660457123142805</v>
       </c>
       <c r="T18">
-        <v>0.514233558269622</v>
+        <v>0.5194093254745605</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.888663145062981</v>
+        <v>8.3658006071181</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07094874412208528</v>
+        <v>0.07087389384428021</v>
       </c>
       <c r="C19">
-        <v>106.156679255709</v>
+        <v>104.9723687417362</v>
       </c>
       <c r="D19">
-        <v>127.072679255709</v>
+        <v>127.1303687417362</v>
       </c>
       <c r="E19">
-        <v>-41.086</v>
+        <v>-39.844</v>
       </c>
       <c r="F19">
-        <v>21.114</v>
+        <v>22.356</v>
       </c>
       <c r="G19">
         <v>0.198</v>
@@ -2827,28 +2827,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M19">
-        <v>1.129599</v>
+        <v>1.196046</v>
       </c>
       <c r="N19">
-        <v>8.320400999999999</v>
+        <v>8.253953999999998</v>
       </c>
       <c r="O19">
-        <v>1.58087619</v>
+        <v>1.56825126</v>
       </c>
       <c r="P19">
-        <v>6.739524809999999</v>
+        <v>6.685702739999998</v>
       </c>
       <c r="Q19">
-        <v>27.03952481</v>
+        <v>26.98570274</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07660457123142805</v>
+        <v>0.07691901688326856</v>
       </c>
       <c r="T19">
-        <v>0.5194093254745605</v>
+        <v>0.5247113309040097</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.3658006071181</v>
+        <v>7.901033906722649</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07087389384428022</v>
+        <v>0.07092216356647515</v>
       </c>
       <c r="C20">
-        <v>104.9723687417361</v>
+        <v>103.6931597379408</v>
       </c>
       <c r="D20">
-        <v>127.1303687417361</v>
+        <v>127.0931597379408</v>
       </c>
       <c r="E20">
-        <v>-39.84400000000001</v>
+        <v>-38.602</v>
       </c>
       <c r="F20">
-        <v>22.356</v>
+        <v>23.598</v>
       </c>
       <c r="G20">
         <v>0.198</v>
@@ -2909,45 +2909,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M20">
-        <v>1.196046</v>
+        <v>1.2813714</v>
       </c>
       <c r="N20">
-        <v>8.253954</v>
+        <v>8.168628599999998</v>
       </c>
       <c r="O20">
-        <v>1.56825126</v>
+        <v>1.552039434</v>
       </c>
       <c r="P20">
-        <v>6.68570274</v>
+        <v>6.616589165999999</v>
       </c>
       <c r="Q20">
-        <v>26.98570274</v>
+        <v>26.916589166</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07691901688326856</v>
+        <v>0.07724122662527796</v>
       </c>
       <c r="T20">
-        <v>0.5247113309040097</v>
+        <v>0.5301442500477662</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.19</v>
       </c>
       <c r="W20">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.901033906722652</v>
+        <v>7.374910974288951</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07092216356647515</v>
+        <v>0.07085379328867009</v>
       </c>
       <c r="C21">
-        <v>103.6931597379408</v>
+        <v>102.5038698013182</v>
       </c>
       <c r="D21">
-        <v>127.0931597379408</v>
+        <v>127.1458698013182</v>
       </c>
       <c r="E21">
-        <v>-38.602</v>
+        <v>-37.36</v>
       </c>
       <c r="F21">
-        <v>23.598</v>
+        <v>24.84</v>
       </c>
       <c r="G21">
         <v>0.198</v>
@@ -2991,28 +2991,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M21">
-        <v>1.2813714</v>
+        <v>1.348812</v>
       </c>
       <c r="N21">
-        <v>8.168628599999998</v>
+        <v>8.101187999999999</v>
       </c>
       <c r="O21">
-        <v>1.552039434</v>
+        <v>1.53922572</v>
       </c>
       <c r="P21">
-        <v>6.616589165999999</v>
+        <v>6.561962279999999</v>
       </c>
       <c r="Q21">
-        <v>26.916589166</v>
+        <v>26.86196228</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07724122662527796</v>
+        <v>0.07757149161083761</v>
       </c>
       <c r="T21">
-        <v>0.5301442500477662</v>
+        <v>0.5357129921701168</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.374910974288951</v>
+        <v>7.006165425574504</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07085379328867009</v>
+        <v>0.07078542301086502</v>
       </c>
       <c r="C22">
-        <v>102.5038698013182</v>
+        <v>101.31462360432</v>
       </c>
       <c r="D22">
-        <v>127.1458698013182</v>
+        <v>127.1986236043201</v>
       </c>
       <c r="E22">
-        <v>-37.36</v>
+        <v>-36.11799999999999</v>
       </c>
       <c r="F22">
-        <v>24.84</v>
+        <v>26.082</v>
       </c>
       <c r="G22">
         <v>0.198</v>
@@ -3073,28 +3073,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M22">
-        <v>1.348812</v>
+        <v>1.4162526</v>
       </c>
       <c r="N22">
-        <v>8.101187999999999</v>
+        <v>8.033747399999999</v>
       </c>
       <c r="O22">
-        <v>1.53922572</v>
+        <v>1.526412006</v>
       </c>
       <c r="P22">
-        <v>6.561962279999999</v>
+        <v>6.507335393999999</v>
       </c>
       <c r="Q22">
-        <v>26.86196228</v>
+        <v>26.807335394</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07757149161083761</v>
+        <v>0.07791011773527218</v>
       </c>
       <c r="T22">
-        <v>0.5357129921701168</v>
+        <v>0.5414227151056914</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.006165425574504</v>
+        <v>6.672538500547147</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07078542301086502</v>
+        <v>0.07071705273305998</v>
       </c>
       <c r="C23">
-        <v>101.31462360432</v>
+        <v>100.1254212014127</v>
       </c>
       <c r="D23">
-        <v>127.1986236043201</v>
+        <v>127.2514212014127</v>
       </c>
       <c r="E23">
-        <v>-36.118</v>
+        <v>-34.876</v>
       </c>
       <c r="F23">
-        <v>26.082</v>
+        <v>27.324</v>
       </c>
       <c r="G23">
         <v>0.198</v>
@@ -3155,28 +3155,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M23">
-        <v>1.4162526</v>
+        <v>1.4836932</v>
       </c>
       <c r="N23">
-        <v>8.033747399999999</v>
+        <v>7.966306799999999</v>
       </c>
       <c r="O23">
-        <v>1.526412006</v>
+        <v>1.513598292</v>
       </c>
       <c r="P23">
-        <v>6.507335393999999</v>
+        <v>6.452708507999999</v>
       </c>
       <c r="Q23">
-        <v>26.807335394</v>
+        <v>26.752708508</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07791011773527218</v>
+        <v>0.07825742658084611</v>
       </c>
       <c r="T23">
-        <v>0.5414227151056914</v>
+        <v>0.5472788411934602</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.672538500547148</v>
+        <v>6.369241295976822</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07071705273305998</v>
+        <v>0.07083498245525489</v>
       </c>
       <c r="C24">
-        <v>100.1254212014127</v>
+        <v>98.79237968296997</v>
       </c>
       <c r="D24">
-        <v>127.2514212014127</v>
+        <v>127.16037968297</v>
       </c>
       <c r="E24">
-        <v>-34.876</v>
+        <v>-33.634</v>
       </c>
       <c r="F24">
-        <v>27.324</v>
+        <v>28.566</v>
       </c>
       <c r="G24">
         <v>0.198</v>
@@ -3237,45 +3237,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M24">
-        <v>1.4836932</v>
+        <v>1.5796998</v>
       </c>
       <c r="N24">
-        <v>7.966306799999999</v>
+        <v>7.870300199999999</v>
       </c>
       <c r="O24">
-        <v>1.513598292</v>
+        <v>1.495357038</v>
       </c>
       <c r="P24">
-        <v>6.452708507999999</v>
+        <v>6.374943161999999</v>
       </c>
       <c r="Q24">
-        <v>26.752708508</v>
+        <v>26.674943162</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07825742658084611</v>
+        <v>0.07861375643539596</v>
       </c>
       <c r="T24">
-        <v>0.5472788411934602</v>
+        <v>0.5532870744523397</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.19</v>
       </c>
       <c r="W24">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.369241295976822</v>
+        <v>5.982149266588499</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07083498245525489</v>
+        <v>0.07077471217744982</v>
       </c>
       <c r="C25">
-        <v>98.79237968296997</v>
+        <v>97.59689193958148</v>
       </c>
       <c r="D25">
-        <v>127.16037968297</v>
+        <v>127.2068919395815</v>
       </c>
       <c r="E25">
-        <v>-33.634</v>
+        <v>-32.392</v>
       </c>
       <c r="F25">
-        <v>28.566</v>
+        <v>29.808</v>
       </c>
       <c r="G25">
         <v>0.198</v>
@@ -3319,28 +3319,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M25">
-        <v>1.5796998</v>
+        <v>1.6483824</v>
       </c>
       <c r="N25">
-        <v>7.870300199999999</v>
+        <v>7.801617599999999</v>
       </c>
       <c r="O25">
-        <v>1.495357038</v>
+        <v>1.482307344</v>
       </c>
       <c r="P25">
-        <v>6.374943161999999</v>
+        <v>6.319310256</v>
       </c>
       <c r="Q25">
-        <v>26.674943162</v>
+        <v>26.619310256</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07861375643539596</v>
+        <v>0.07897946339138134</v>
       </c>
       <c r="T25">
-        <v>0.5532870744523397</v>
+        <v>0.5594534191127688</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.982149266588499</v>
+        <v>5.732893047147312</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07077471217744982</v>
+        <v>0.07071444189964476</v>
       </c>
       <c r="C26">
-        <v>97.5968919395815</v>
+        <v>96.40143823480831</v>
       </c>
       <c r="D26">
-        <v>127.2068919395815</v>
+        <v>127.2534382348083</v>
       </c>
       <c r="E26">
-        <v>-32.392</v>
+        <v>-31.15</v>
       </c>
       <c r="F26">
-        <v>29.808</v>
+        <v>31.05</v>
       </c>
       <c r="G26">
         <v>0.198</v>
@@ -3401,28 +3401,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M26">
-        <v>1.6483824</v>
+        <v>1.717065</v>
       </c>
       <c r="N26">
-        <v>7.801617599999999</v>
+        <v>7.732934999999999</v>
       </c>
       <c r="O26">
-        <v>1.482307344</v>
+        <v>1.46925765</v>
       </c>
       <c r="P26">
-        <v>6.319310256</v>
+        <v>6.26367735</v>
       </c>
       <c r="Q26">
-        <v>26.619310256</v>
+        <v>26.56367735</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07897946339138134</v>
+        <v>0.07935492253285968</v>
       </c>
       <c r="T26">
-        <v>0.5594534191127688</v>
+        <v>0.5657841996308094</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.732893047147312</v>
+        <v>5.50357732526142</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07071444189964476</v>
+        <v>0.07065417162183969</v>
       </c>
       <c r="C27">
-        <v>96.40143823480831</v>
+        <v>95.20601860602928</v>
       </c>
       <c r="D27">
-        <v>127.2534382348083</v>
+        <v>127.3000186060293</v>
       </c>
       <c r="E27">
-        <v>-31.15</v>
+        <v>-29.908</v>
       </c>
       <c r="F27">
-        <v>31.05</v>
+        <v>32.292</v>
       </c>
       <c r="G27">
         <v>0.198</v>
@@ -3483,28 +3483,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M27">
-        <v>1.717065</v>
+        <v>1.7857476</v>
       </c>
       <c r="N27">
-        <v>7.732934999999999</v>
+        <v>7.664252399999999</v>
       </c>
       <c r="O27">
-        <v>1.46925765</v>
+        <v>1.456207956</v>
       </c>
       <c r="P27">
-        <v>6.26367735</v>
+        <v>6.208044443999999</v>
       </c>
       <c r="Q27">
-        <v>26.56367735</v>
+        <v>26.508044444</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07935492253285968</v>
+        <v>0.07974052921870228</v>
       </c>
       <c r="T27">
-        <v>0.5657841996308094</v>
+        <v>0.5722860823250132</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.50357732526142</v>
+        <v>5.291901274289826</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07065417162183969</v>
+        <v>0.07059390134403462</v>
       </c>
       <c r="C28">
-        <v>95.20601860602928</v>
+        <v>94.0106330906781</v>
       </c>
       <c r="D28">
-        <v>127.3000186060293</v>
+        <v>127.3466330906781</v>
       </c>
       <c r="E28">
-        <v>-29.908</v>
+        <v>-28.666</v>
       </c>
       <c r="F28">
-        <v>32.292</v>
+        <v>33.53400000000001</v>
       </c>
       <c r="G28">
         <v>0.198</v>
@@ -3565,28 +3565,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M28">
-        <v>1.7857476</v>
+        <v>1.8544302</v>
       </c>
       <c r="N28">
-        <v>7.664252399999999</v>
+        <v>7.595569799999999</v>
       </c>
       <c r="O28">
-        <v>1.456207956</v>
+        <v>1.443158262</v>
       </c>
       <c r="P28">
-        <v>6.208044443999999</v>
+        <v>6.152411537999999</v>
       </c>
       <c r="Q28">
-        <v>26.508044444</v>
+        <v>26.452411538</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07974052921870228</v>
+        <v>0.08013670047128031</v>
       </c>
       <c r="T28">
-        <v>0.5722860823250132</v>
+        <v>0.5789660987916609</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.291901274289826</v>
+        <v>5.09590493079761</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07059390134403462</v>
+        <v>0.07053363106622955</v>
       </c>
       <c r="C29">
-        <v>94.0106330906781</v>
+        <v>92.81528172624326</v>
       </c>
       <c r="D29">
-        <v>127.3466330906781</v>
+        <v>127.3932817262433</v>
       </c>
       <c r="E29">
-        <v>-28.666</v>
+        <v>-27.424</v>
       </c>
       <c r="F29">
-        <v>33.53400000000001</v>
+        <v>34.776</v>
       </c>
       <c r="G29">
         <v>0.198</v>
@@ -3647,28 +3647,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M29">
-        <v>1.8544302</v>
+        <v>1.9231128</v>
       </c>
       <c r="N29">
-        <v>7.595569799999999</v>
+        <v>7.526887199999999</v>
       </c>
       <c r="O29">
-        <v>1.443158262</v>
+        <v>1.430108568</v>
       </c>
       <c r="P29">
-        <v>6.152411537999999</v>
+        <v>6.096778631999999</v>
       </c>
       <c r="Q29">
-        <v>26.452411538</v>
+        <v>26.396778632</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08013670047128031</v>
+        <v>0.08054387648087438</v>
       </c>
       <c r="T29">
-        <v>0.5789660987916609</v>
+        <v>0.5858316712712711</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.09590493079761</v>
+        <v>4.913908326126267</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07053363106622955</v>
+        <v>0.07047336078842451</v>
       </c>
       <c r="C30">
-        <v>92.81528172624326</v>
+        <v>91.61996455026821</v>
       </c>
       <c r="D30">
-        <v>127.3932817262433</v>
+        <v>127.4399645502682</v>
       </c>
       <c r="E30">
-        <v>-27.424</v>
+        <v>-26.182</v>
       </c>
       <c r="F30">
-        <v>34.776</v>
+        <v>36.01800000000001</v>
       </c>
       <c r="G30">
         <v>0.198</v>
@@ -3729,28 +3729,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M30">
-        <v>1.9231128</v>
+        <v>1.9917954</v>
       </c>
       <c r="N30">
-        <v>7.526887199999999</v>
+        <v>7.458204599999998</v>
       </c>
       <c r="O30">
-        <v>1.430108568</v>
+        <v>1.417058874</v>
       </c>
       <c r="P30">
-        <v>6.096778631999999</v>
+        <v>6.041145725999999</v>
       </c>
       <c r="Q30">
-        <v>26.396778632</v>
+        <v>26.341145726</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08054387648087438</v>
+        <v>0.08096252223721762</v>
       </c>
       <c r="T30">
-        <v>0.5858316712712711</v>
+        <v>0.5928906401587578</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.913908326126267</v>
+        <v>4.744463211432257</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07047336078842449</v>
+        <v>0.07041309051061943</v>
       </c>
       <c r="C31">
-        <v>91.61996455026824</v>
+        <v>90.42468160035148</v>
       </c>
       <c r="D31">
-        <v>127.4399645502682</v>
+        <v>127.4866816003515</v>
       </c>
       <c r="E31">
-        <v>-26.182</v>
+        <v>-24.94</v>
       </c>
       <c r="F31">
-        <v>36.018</v>
+        <v>37.26</v>
       </c>
       <c r="G31">
         <v>0.198</v>
@@ -3811,28 +3811,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M31">
-        <v>1.9917954</v>
+        <v>2.060478</v>
       </c>
       <c r="N31">
-        <v>7.458204599999999</v>
+        <v>7.389521999999999</v>
       </c>
       <c r="O31">
-        <v>1.417058874</v>
+        <v>1.40400918</v>
       </c>
       <c r="P31">
-        <v>6.041145726</v>
+        <v>5.985512819999999</v>
       </c>
       <c r="Q31">
-        <v>26.341145726</v>
+        <v>26.28551282</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0809625222372176</v>
+        <v>0.08139312930088491</v>
       </c>
       <c r="T31">
-        <v>0.5928906401587577</v>
+        <v>0.6001512938716009</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.744463211432258</v>
+        <v>4.58631443771785</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07041309051061943</v>
+        <v>0.07098057023281436</v>
       </c>
       <c r="C32">
-        <v>90.42468160035148</v>
+        <v>88.74416572231701</v>
       </c>
       <c r="D32">
-        <v>127.4866816003515</v>
+        <v>127.048165722317</v>
       </c>
       <c r="E32">
-        <v>-24.94</v>
+        <v>-23.698</v>
       </c>
       <c r="F32">
-        <v>37.26</v>
+        <v>38.502</v>
       </c>
       <c r="G32">
         <v>0.198</v>
@@ -3893,45 +3893,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M32">
-        <v>2.060478</v>
+        <v>2.2254156</v>
       </c>
       <c r="N32">
-        <v>7.389521999999999</v>
+        <v>7.224584399999999</v>
       </c>
       <c r="O32">
-        <v>1.40400918</v>
+        <v>1.372671036</v>
       </c>
       <c r="P32">
-        <v>5.985512819999999</v>
+        <v>5.851913364</v>
       </c>
       <c r="Q32">
-        <v>26.28551282</v>
+        <v>26.151913364</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08139312930088491</v>
+        <v>0.08183621772871646</v>
       </c>
       <c r="T32">
-        <v>0.6001512938716009</v>
+        <v>0.6076224013152514</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.19</v>
       </c>
       <c r="W32">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.58631443771785</v>
+        <v>4.246397841373988</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07098057023281436</v>
+        <v>0.0709405499550093</v>
       </c>
       <c r="C33">
-        <v>88.74416572231701</v>
+        <v>87.53299220823396</v>
       </c>
       <c r="D33">
-        <v>127.048165722317</v>
+        <v>127.078992208234</v>
       </c>
       <c r="E33">
-        <v>-23.698</v>
+        <v>-22.456</v>
       </c>
       <c r="F33">
-        <v>38.502</v>
+        <v>39.744</v>
       </c>
       <c r="G33">
         <v>0.198</v>
@@ -3975,28 +3975,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M33">
-        <v>2.2254156</v>
+        <v>2.2972032</v>
       </c>
       <c r="N33">
-        <v>7.224584399999999</v>
+        <v>7.152796799999999</v>
       </c>
       <c r="O33">
-        <v>1.372671036</v>
+        <v>1.359031392</v>
       </c>
       <c r="P33">
-        <v>5.851913364</v>
+        <v>5.793765407999999</v>
       </c>
       <c r="Q33">
-        <v>26.151913364</v>
+        <v>26.093765408</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08183621772871646</v>
+        <v>0.08229233816913133</v>
       </c>
       <c r="T33">
-        <v>0.6076224013152514</v>
+        <v>0.6153132472131267</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.246397841373988</v>
+        <v>4.113697908831051</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0709405499550093</v>
+        <v>0.07183607967720423</v>
       </c>
       <c r="C34">
-        <v>87.53299220823396</v>
+        <v>85.60474958691835</v>
       </c>
       <c r="D34">
-        <v>127.078992208234</v>
+        <v>126.3927495869184</v>
       </c>
       <c r="E34">
-        <v>-22.456</v>
+        <v>-21.214</v>
       </c>
       <c r="F34">
-        <v>39.744</v>
+        <v>40.986</v>
       </c>
       <c r="G34">
         <v>0.198</v>
@@ -4057,45 +4057,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M34">
-        <v>2.2972032</v>
+        <v>2.5124418</v>
       </c>
       <c r="N34">
-        <v>7.152796799999999</v>
+        <v>6.937558199999999</v>
       </c>
       <c r="O34">
-        <v>1.359031392</v>
+        <v>1.318136058</v>
       </c>
       <c r="P34">
-        <v>5.793765407999999</v>
+        <v>5.619422141999999</v>
       </c>
       <c r="Q34">
-        <v>26.093765408</v>
+        <v>25.919422142</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08229233816913133</v>
+        <v>0.08276207414508094</v>
       </c>
       <c r="T34">
-        <v>0.6153132472131267</v>
+        <v>0.6232336706004908</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.19</v>
       </c>
       <c r="W34">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.113697908831051</v>
+        <v>3.761281156841125</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07183607967720423</v>
+        <v>0.07182440939939917</v>
       </c>
       <c r="C35">
-        <v>85.60474958691835</v>
+        <v>84.37164483041792</v>
       </c>
       <c r="D35">
-        <v>126.3927495869184</v>
+        <v>126.4016448304179</v>
       </c>
       <c r="E35">
-        <v>-21.214</v>
+        <v>-19.972</v>
       </c>
       <c r="F35">
-        <v>40.986</v>
+        <v>42.228</v>
       </c>
       <c r="G35">
         <v>0.198</v>
@@ -4139,28 +4139,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M35">
-        <v>2.5124418</v>
+        <v>2.5885764</v>
       </c>
       <c r="N35">
-        <v>6.937558199999999</v>
+        <v>6.861423599999999</v>
       </c>
       <c r="O35">
-        <v>1.318136058</v>
+        <v>1.303670484</v>
       </c>
       <c r="P35">
-        <v>5.619422141999999</v>
+        <v>5.557753115999999</v>
       </c>
       <c r="Q35">
-        <v>25.919422142</v>
+        <v>25.857753116</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08276207414508094</v>
+        <v>0.08324604454454421</v>
       </c>
       <c r="T35">
-        <v>0.6232336706004908</v>
+        <v>0.6313941068177752</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.761281156841125</v>
+        <v>3.650655240463445</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07182440939939917</v>
+        <v>0.0718127391215941</v>
       </c>
       <c r="C36">
-        <v>84.37164483041792</v>
+        <v>83.13854132606096</v>
       </c>
       <c r="D36">
-        <v>126.4016448304179</v>
+        <v>126.410541326061</v>
       </c>
       <c r="E36">
-        <v>-19.972</v>
+        <v>-18.73</v>
       </c>
       <c r="F36">
-        <v>42.228</v>
+        <v>43.47000000000001</v>
       </c>
       <c r="G36">
         <v>0.198</v>
@@ -4221,28 +4221,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M36">
-        <v>2.5885764</v>
+        <v>2.664711</v>
       </c>
       <c r="N36">
-        <v>6.861423599999999</v>
+        <v>6.785288999999999</v>
       </c>
       <c r="O36">
-        <v>1.303670484</v>
+        <v>1.28920491</v>
       </c>
       <c r="P36">
-        <v>5.557753115999999</v>
+        <v>5.496084089999999</v>
       </c>
       <c r="Q36">
-        <v>25.857753116</v>
+        <v>25.79608409</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08324604454454421</v>
+        <v>0.083744906340914</v>
       </c>
       <c r="T36">
-        <v>0.6313941068177752</v>
+        <v>0.6398056333802066</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.650655240463445</v>
+        <v>3.546350805021632</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0718127391215941</v>
+        <v>0.07261754884378904</v>
       </c>
       <c r="C37">
-        <v>83.13854132606096</v>
+        <v>81.28593866289579</v>
       </c>
       <c r="D37">
-        <v>126.410541326061</v>
+        <v>125.7999386628958</v>
       </c>
       <c r="E37">
-        <v>-18.73</v>
+        <v>-17.488</v>
       </c>
       <c r="F37">
-        <v>43.47000000000001</v>
+        <v>44.712</v>
       </c>
       <c r="G37">
         <v>0.198</v>
@@ -4303,45 +4303,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M37">
-        <v>2.664711</v>
+        <v>2.8660392</v>
       </c>
       <c r="N37">
-        <v>6.785288999999999</v>
+        <v>6.583960799999999</v>
       </c>
       <c r="O37">
-        <v>1.28920491</v>
+        <v>1.250952552</v>
       </c>
       <c r="P37">
-        <v>5.496084089999999</v>
+        <v>5.333008247999999</v>
       </c>
       <c r="Q37">
-        <v>25.79608409</v>
+        <v>25.633008248</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.083744906340914</v>
+        <v>0.08425935756842037</v>
       </c>
       <c r="T37">
-        <v>0.6398056333802066</v>
+        <v>0.6484800201477142</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.19</v>
       </c>
       <c r="W37">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.546350805021632</v>
+        <v>3.297233338608906</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07261754884378904</v>
+        <v>0.07262855856598398</v>
       </c>
       <c r="C38">
-        <v>81.2859386628958</v>
+        <v>80.03562657202286</v>
       </c>
       <c r="D38">
-        <v>125.7999386628958</v>
+        <v>125.7916265720229</v>
       </c>
       <c r="E38">
-        <v>-17.48800000000001</v>
+        <v>-16.246</v>
       </c>
       <c r="F38">
-        <v>44.712</v>
+        <v>45.954</v>
       </c>
       <c r="G38">
         <v>0.198</v>
@@ -4385,28 +4385,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M38">
-        <v>2.8660392</v>
+        <v>2.9456514</v>
       </c>
       <c r="N38">
-        <v>6.5839608</v>
+        <v>6.504348599999999</v>
       </c>
       <c r="O38">
-        <v>1.250952552</v>
+        <v>1.235826234</v>
       </c>
       <c r="P38">
-        <v>5.333008248</v>
+        <v>5.268522365999999</v>
       </c>
       <c r="Q38">
-        <v>25.633008248</v>
+        <v>25.568522366</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08425935756842037</v>
+        <v>0.08479014058092695</v>
       </c>
       <c r="T38">
-        <v>0.6484800201477141</v>
+        <v>0.6574297842729203</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.297233338608907</v>
+        <v>3.208118924051909</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07262855856598398</v>
+        <v>0.07263956828817891</v>
       </c>
       <c r="C39">
-        <v>80.03562657202286</v>
+        <v>78.78531557950166</v>
       </c>
       <c r="D39">
-        <v>125.7916265720229</v>
+        <v>125.7833155795017</v>
       </c>
       <c r="E39">
-        <v>-16.246</v>
+        <v>-15.004</v>
       </c>
       <c r="F39">
-        <v>45.954</v>
+        <v>47.19600000000001</v>
       </c>
       <c r="G39">
         <v>0.198</v>
@@ -4467,28 +4467,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M39">
-        <v>2.9456514</v>
+        <v>3.025263600000001</v>
       </c>
       <c r="N39">
-        <v>6.504348599999999</v>
+        <v>6.424736399999999</v>
       </c>
       <c r="O39">
-        <v>1.235826234</v>
+        <v>1.220699916</v>
       </c>
       <c r="P39">
-        <v>5.268522365999999</v>
+        <v>5.204036483999999</v>
       </c>
       <c r="Q39">
-        <v>25.568522366</v>
+        <v>25.504036484</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08479014058092695</v>
+        <v>0.08533804562609501</v>
       </c>
       <c r="T39">
-        <v>0.6574297842729203</v>
+        <v>0.6666682504666814</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.208118924051909</v>
+        <v>3.123694741840016</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07263956828817891</v>
+        <v>0.07265057801037383</v>
       </c>
       <c r="C40">
-        <v>78.78531557950166</v>
+        <v>77.53500568511447</v>
       </c>
       <c r="D40">
-        <v>125.7833155795017</v>
+        <v>125.7750056851145</v>
       </c>
       <c r="E40">
-        <v>-15.004</v>
+        <v>-13.762</v>
       </c>
       <c r="F40">
-        <v>47.19600000000001</v>
+        <v>48.438</v>
       </c>
       <c r="G40">
         <v>0.198</v>
@@ -4549,28 +4549,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M40">
-        <v>3.025263600000001</v>
+        <v>3.1048758</v>
       </c>
       <c r="N40">
-        <v>6.424736399999999</v>
+        <v>6.345124199999999</v>
       </c>
       <c r="O40">
-        <v>1.220699916</v>
+        <v>1.205573598</v>
       </c>
       <c r="P40">
-        <v>5.204036483999999</v>
+        <v>5.139550601999999</v>
       </c>
       <c r="Q40">
-        <v>25.504036484</v>
+        <v>25.439550602</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08533804562609501</v>
+        <v>0.08590391477110465</v>
       </c>
       <c r="T40">
-        <v>0.6666682504666814</v>
+        <v>0.6762096171913856</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.123694741840016</v>
+        <v>3.043600004869759</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07265057801037383</v>
+        <v>0.07518878773256878</v>
       </c>
       <c r="C41">
-        <v>77.53500568511447</v>
+        <v>74.40608712691275</v>
       </c>
       <c r="D41">
-        <v>125.7750056851145</v>
+        <v>123.8880871269128</v>
       </c>
       <c r="E41">
-        <v>-13.762</v>
+        <v>-12.52</v>
       </c>
       <c r="F41">
-        <v>48.438</v>
+        <v>49.68000000000001</v>
       </c>
       <c r="G41">
         <v>0.198</v>
@@ -4631,45 +4631,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M41">
-        <v>3.1048758</v>
+        <v>3.571992000000001</v>
       </c>
       <c r="N41">
-        <v>6.345124199999999</v>
+        <v>5.878007999999999</v>
       </c>
       <c r="O41">
-        <v>1.205573598</v>
+        <v>1.11682152</v>
       </c>
       <c r="P41">
-        <v>5.139550601999999</v>
+        <v>4.761186479999999</v>
       </c>
       <c r="Q41">
-        <v>25.439550602</v>
+        <v>25.06118648</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08590391477110465</v>
+        <v>0.08648864622094796</v>
       </c>
       <c r="T41">
-        <v>0.6762096171913856</v>
+        <v>0.6860690294735799</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.19</v>
       </c>
       <c r="W41">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.043600004869759</v>
+        <v>2.645582632883835</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07518878773256878</v>
+        <v>0.07526297745476371</v>
       </c>
       <c r="C42">
-        <v>74.40608712691275</v>
+        <v>73.10978533009575</v>
       </c>
       <c r="D42">
-        <v>123.8880871269128</v>
+        <v>123.8337853300958</v>
       </c>
       <c r="E42">
-        <v>-12.52</v>
+        <v>-11.278</v>
       </c>
       <c r="F42">
-        <v>49.68000000000001</v>
+        <v>50.922</v>
       </c>
       <c r="G42">
         <v>0.198</v>
@@ -4713,28 +4713,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M42">
-        <v>3.571992000000001</v>
+        <v>3.661291800000001</v>
       </c>
       <c r="N42">
-        <v>5.878007999999999</v>
+        <v>5.788708199999999</v>
       </c>
       <c r="O42">
-        <v>1.11682152</v>
+        <v>1.099854558</v>
       </c>
       <c r="P42">
-        <v>4.761186479999999</v>
+        <v>4.688853641999999</v>
       </c>
       <c r="Q42">
-        <v>25.06118648</v>
+        <v>24.988853642</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08648864622094796</v>
+        <v>0.08709319907587069</v>
       </c>
       <c r="T42">
-        <v>0.6860690294735799</v>
+        <v>0.6962626591212724</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.645582632883835</v>
+        <v>2.581056227203742</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07526297745476371</v>
+        <v>0.07533716717695864</v>
       </c>
       <c r="C43">
-        <v>73.10978533009575</v>
+        <v>71.81353111482306</v>
       </c>
       <c r="D43">
-        <v>123.8337853300958</v>
+        <v>123.7795311148231</v>
       </c>
       <c r="E43">
-        <v>-11.278</v>
+        <v>-10.03599999999999</v>
       </c>
       <c r="F43">
-        <v>50.922</v>
+        <v>52.16400000000001</v>
       </c>
       <c r="G43">
         <v>0.198</v>
@@ -4795,28 +4795,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M43">
-        <v>3.661291800000001</v>
+        <v>3.750591600000001</v>
       </c>
       <c r="N43">
-        <v>5.788708199999999</v>
+        <v>5.699408399999998</v>
       </c>
       <c r="O43">
-        <v>1.099854558</v>
+        <v>1.082887596</v>
       </c>
       <c r="P43">
-        <v>4.688853641999999</v>
+        <v>4.616520803999999</v>
       </c>
       <c r="Q43">
-        <v>24.988853642</v>
+        <v>24.916520804</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08709319907587069</v>
+        <v>0.08771859858096318</v>
       </c>
       <c r="T43">
-        <v>0.6962626591212724</v>
+        <v>0.7068077932395749</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.581056227203742</v>
+        <v>2.519602507508415</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07533716717695865</v>
+        <v>0.07676972689915358</v>
       </c>
       <c r="C44">
-        <v>71.81353111482308</v>
+        <v>69.53315773793099</v>
       </c>
       <c r="D44">
-        <v>123.7795311148231</v>
+        <v>122.741157737931</v>
       </c>
       <c r="E44">
-        <v>-10.036</v>
+        <v>-8.794000000000004</v>
       </c>
       <c r="F44">
-        <v>52.164</v>
+        <v>53.406</v>
       </c>
       <c r="G44">
         <v>0.198</v>
@@ -4877,45 +4877,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M44">
-        <v>3.7505916</v>
+        <v>4.0481748</v>
       </c>
       <c r="N44">
-        <v>5.699408399999999</v>
+        <v>5.401825199999999</v>
       </c>
       <c r="O44">
-        <v>1.082887596</v>
+        <v>1.026346788</v>
       </c>
       <c r="P44">
-        <v>4.616520803999999</v>
+        <v>4.375478412</v>
       </c>
       <c r="Q44">
-        <v>24.916520804</v>
+        <v>24.675478412</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08771859858096318</v>
+        <v>0.0883659419283396</v>
       </c>
       <c r="T44">
-        <v>0.7068077932395748</v>
+        <v>0.7177229320637826</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.19</v>
       </c>
       <c r="W44">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.519602507508415</v>
+        <v>2.334385363003594</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07676972689915358</v>
+        <v>0.07687550662134851</v>
       </c>
       <c r="C45">
-        <v>69.53315773793099</v>
+        <v>68.21517487040362</v>
       </c>
       <c r="D45">
-        <v>122.741157737931</v>
+        <v>122.6651748704036</v>
       </c>
       <c r="E45">
-        <v>-8.794000000000004</v>
+        <v>-7.552</v>
       </c>
       <c r="F45">
-        <v>53.406</v>
+        <v>54.648</v>
       </c>
       <c r="G45">
         <v>0.198</v>
@@ -4959,28 +4959,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M45">
-        <v>4.0481748</v>
+        <v>4.142318400000001</v>
       </c>
       <c r="N45">
-        <v>5.401825199999999</v>
+        <v>5.307681599999999</v>
       </c>
       <c r="O45">
-        <v>1.026346788</v>
+        <v>1.008459504</v>
       </c>
       <c r="P45">
-        <v>4.375478412</v>
+        <v>4.299222095999999</v>
       </c>
       <c r="Q45">
-        <v>24.675478412</v>
+        <v>24.599222096</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0883659419283396</v>
+        <v>0.08903640468097948</v>
       </c>
       <c r="T45">
-        <v>0.7177229320637826</v>
+        <v>0.7290278972745694</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.334385363003594</v>
+        <v>2.281331150208057</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07687550662134851</v>
+        <v>0.07698128634354345</v>
       </c>
       <c r="C46">
-        <v>68.21517487040362</v>
+        <v>66.89728601900667</v>
       </c>
       <c r="D46">
-        <v>122.6651748704036</v>
+        <v>122.5892860190067</v>
       </c>
       <c r="E46">
-        <v>-7.552</v>
+        <v>-6.310000000000002</v>
       </c>
       <c r="F46">
-        <v>54.648</v>
+        <v>55.89</v>
       </c>
       <c r="G46">
         <v>0.198</v>
@@ -5041,28 +5041,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M46">
-        <v>4.142318400000001</v>
+        <v>4.236462</v>
       </c>
       <c r="N46">
-        <v>5.307681599999999</v>
+        <v>5.213537999999999</v>
       </c>
       <c r="O46">
-        <v>1.008459504</v>
+        <v>0.9905722199999998</v>
       </c>
       <c r="P46">
-        <v>4.299222095999999</v>
+        <v>4.222965779999999</v>
       </c>
       <c r="Q46">
-        <v>24.599222096</v>
+        <v>24.52296578</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08903640468097948</v>
+        <v>0.08973124789735171</v>
       </c>
       <c r="T46">
-        <v>0.7290278972745694</v>
+        <v>0.7407439521293846</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.281331150208057</v>
+        <v>2.230634902425656</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07698128634354345</v>
+        <v>0.07708706606573838</v>
       </c>
       <c r="C47">
-        <v>66.89728601900667</v>
+        <v>65.57949100935416</v>
       </c>
       <c r="D47">
-        <v>122.5892860190067</v>
+        <v>122.5134910093542</v>
       </c>
       <c r="E47">
-        <v>-6.310000000000002</v>
+        <v>-5.067999999999998</v>
       </c>
       <c r="F47">
-        <v>55.89</v>
+        <v>57.13200000000001</v>
       </c>
       <c r="G47">
         <v>0.198</v>
@@ -5123,28 +5123,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M47">
-        <v>4.236462</v>
+        <v>4.330605600000001</v>
       </c>
       <c r="N47">
-        <v>5.213537999999999</v>
+        <v>5.119394399999998</v>
       </c>
       <c r="O47">
-        <v>0.9905722199999998</v>
+        <v>0.9726849359999997</v>
       </c>
       <c r="P47">
-        <v>4.222965779999999</v>
+        <v>4.146709463999999</v>
       </c>
       <c r="Q47">
-        <v>24.52296578</v>
+        <v>24.446709464</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08973124789735171</v>
+        <v>0.09045182604766366</v>
       </c>
       <c r="T47">
-        <v>0.7407439521293846</v>
+        <v>0.7528939349417857</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.230634902425656</v>
+        <v>2.182142839329446</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07708706606573838</v>
+        <v>0.07719284578793333</v>
       </c>
       <c r="C48">
-        <v>65.57949100935416</v>
+        <v>64.26178966749106</v>
       </c>
       <c r="D48">
-        <v>122.5134910093542</v>
+        <v>122.4377896674911</v>
       </c>
       <c r="E48">
-        <v>-5.067999999999998</v>
+        <v>-3.826000000000001</v>
       </c>
       <c r="F48">
-        <v>57.13200000000001</v>
+        <v>58.374</v>
       </c>
       <c r="G48">
         <v>0.198</v>
@@ -5205,28 +5205,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M48">
-        <v>4.330605600000001</v>
+        <v>4.424749200000001</v>
       </c>
       <c r="N48">
-        <v>5.119394399999998</v>
+        <v>5.025250799999998</v>
       </c>
       <c r="O48">
-        <v>0.9726849359999997</v>
+        <v>0.9547976519999998</v>
       </c>
       <c r="P48">
-        <v>4.146709463999999</v>
+        <v>4.070453147999999</v>
       </c>
       <c r="Q48">
-        <v>24.446709464</v>
+        <v>24.370453148</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09045182604766366</v>
+        <v>0.09119959582628928</v>
       </c>
       <c r="T48">
-        <v>0.7528939349417857</v>
+        <v>0.7655024076716359</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.182142839329446</v>
+        <v>2.135714268279883</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07719284578793333</v>
+        <v>0.07729862551012827</v>
       </c>
       <c r="C49">
-        <v>64.26178966749106</v>
+        <v>62.94418181989199</v>
       </c>
       <c r="D49">
-        <v>122.4377896674911</v>
+        <v>122.362181819892</v>
       </c>
       <c r="E49">
-        <v>-3.826000000000001</v>
+        <v>-2.583999999999996</v>
       </c>
       <c r="F49">
-        <v>58.374</v>
+        <v>59.61600000000001</v>
       </c>
       <c r="G49">
         <v>0.198</v>
@@ -5287,28 +5287,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M49">
-        <v>4.424749200000001</v>
+        <v>4.518892800000001</v>
       </c>
       <c r="N49">
-        <v>5.025250799999998</v>
+        <v>4.931107199999999</v>
       </c>
       <c r="O49">
-        <v>0.9547976519999998</v>
+        <v>0.9369103679999997</v>
       </c>
       <c r="P49">
-        <v>4.070453147999999</v>
+        <v>3.994196831999999</v>
       </c>
       <c r="Q49">
-        <v>24.370453148</v>
+        <v>24.294196832</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09119959582628928</v>
+        <v>0.09197612598101587</v>
       </c>
       <c r="T49">
-        <v>0.7655024076716359</v>
+        <v>0.7785958216603265</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.135714268279883</v>
+        <v>2.091220221024052</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07729862551012825</v>
+        <v>0.0774044052323232</v>
       </c>
       <c r="C50">
-        <v>62.94418181989201</v>
+        <v>61.62666729346002</v>
       </c>
       <c r="D50">
-        <v>122.362181819892</v>
+        <v>122.28666729346</v>
       </c>
       <c r="E50">
-        <v>-2.584000000000003</v>
+        <v>-1.342000000000006</v>
       </c>
       <c r="F50">
-        <v>59.616</v>
+        <v>60.858</v>
       </c>
       <c r="G50">
         <v>0.198</v>
@@ -5369,28 +5369,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M50">
-        <v>4.518892800000001</v>
+        <v>4.6130364</v>
       </c>
       <c r="N50">
-        <v>4.931107199999999</v>
+        <v>4.836963599999999</v>
       </c>
       <c r="O50">
-        <v>0.9369103679999997</v>
+        <v>0.9190230839999998</v>
       </c>
       <c r="P50">
-        <v>3.994196831999999</v>
+        <v>3.917940515999999</v>
       </c>
       <c r="Q50">
-        <v>24.294196832</v>
+        <v>24.217940516</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09197612598101586</v>
+        <v>0.09278310829867291</v>
       </c>
       <c r="T50">
-        <v>0.7785958216603264</v>
+        <v>0.7922027028642598</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.091220221024052</v>
+        <v>2.048542257329684</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0774044052323232</v>
+        <v>0.07751018495451813</v>
       </c>
       <c r="C51">
-        <v>61.62666729346002</v>
+        <v>60.30924591552515</v>
       </c>
       <c r="D51">
-        <v>122.28666729346</v>
+        <v>122.2112459155252</v>
       </c>
       <c r="E51">
-        <v>-1.342000000000006</v>
+        <v>-0.1000000000000014</v>
       </c>
       <c r="F51">
-        <v>60.858</v>
+        <v>62.1</v>
       </c>
       <c r="G51">
         <v>0.198</v>
@@ -5451,28 +5451,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M51">
-        <v>4.6130364</v>
+        <v>4.70718</v>
       </c>
       <c r="N51">
-        <v>4.836963599999999</v>
+        <v>4.742819999999999</v>
       </c>
       <c r="O51">
-        <v>0.9190230839999998</v>
+        <v>0.9011357999999998</v>
       </c>
       <c r="P51">
-        <v>3.917940515999999</v>
+        <v>3.8416842</v>
       </c>
       <c r="Q51">
-        <v>24.217940516</v>
+        <v>24.1416842</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09278310829867291</v>
+        <v>0.09362236990903625</v>
       </c>
       <c r="T51">
-        <v>0.7922027028642598</v>
+        <v>0.8063538593163504</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.048542257329684</v>
+        <v>2.00757141218309</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07751018495451813</v>
+        <v>0.08348198467671306</v>
       </c>
       <c r="C52">
-        <v>60.30924591552515</v>
+        <v>54.95513443360137</v>
       </c>
       <c r="D52">
-        <v>122.2112459155252</v>
+        <v>118.0991344336014</v>
       </c>
       <c r="E52">
-        <v>-0.1000000000000014</v>
+        <v>1.142000000000003</v>
       </c>
       <c r="F52">
-        <v>62.1</v>
+        <v>63.34200000000001</v>
       </c>
       <c r="G52">
         <v>0.198</v>
@@ -5533,45 +5533,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M52">
-        <v>4.70718</v>
+        <v>5.70078</v>
       </c>
       <c r="N52">
-        <v>4.742819999999999</v>
+        <v>3.749219999999999</v>
       </c>
       <c r="O52">
-        <v>0.9011357999999998</v>
+        <v>0.7123517999999999</v>
       </c>
       <c r="P52">
-        <v>3.8416842</v>
+        <v>3.036868199999999</v>
       </c>
       <c r="Q52">
-        <v>24.1416842</v>
+        <v>23.3368682</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09362236990903625</v>
+        <v>0.09449588709533277</v>
       </c>
       <c r="T52">
-        <v>0.8063538593163504</v>
+        <v>0.8210826139909755</v>
       </c>
       <c r="U52">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V52">
         <v>0.19</v>
       </c>
       <c r="W52">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.00757141218309</v>
+        <v>1.657667898077105</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08348198467671306</v>
+        <v>0.08370278439890799</v>
       </c>
       <c r="C53">
-        <v>54.95513443360137</v>
+        <v>53.5663926640682</v>
       </c>
       <c r="D53">
-        <v>118.0991344336014</v>
+        <v>117.9523926640682</v>
       </c>
       <c r="E53">
-        <v>1.142000000000003</v>
+        <v>2.384</v>
       </c>
       <c r="F53">
-        <v>63.34200000000001</v>
+        <v>64.584</v>
       </c>
       <c r="G53">
         <v>0.198</v>
@@ -5615,28 +5615,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M53">
-        <v>5.70078</v>
+        <v>5.81256</v>
       </c>
       <c r="N53">
-        <v>3.749219999999999</v>
+        <v>3.637439999999999</v>
       </c>
       <c r="O53">
-        <v>0.7123517999999999</v>
+        <v>0.6911135999999998</v>
       </c>
       <c r="P53">
-        <v>3.036868199999999</v>
+        <v>2.946326399999999</v>
       </c>
       <c r="Q53">
-        <v>23.3368682</v>
+        <v>23.2463264</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09449588709533277</v>
+        <v>0.09540580083105832</v>
       </c>
       <c r="T53">
-        <v>0.8210826139909755</v>
+        <v>0.8364250667770431</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.657667898077105</v>
+        <v>1.62578966926793</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08370278439890799</v>
+        <v>0.08392358412110293</v>
       </c>
       <c r="C54">
-        <v>53.5663926640682</v>
+        <v>52.17801510422446</v>
       </c>
       <c r="D54">
-        <v>117.9523926640682</v>
+        <v>117.8060151042245</v>
       </c>
       <c r="E54">
-        <v>2.384</v>
+        <v>3.626000000000005</v>
       </c>
       <c r="F54">
-        <v>64.584</v>
+        <v>65.82600000000001</v>
       </c>
       <c r="G54">
         <v>0.198</v>
@@ -5697,28 +5697,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M54">
-        <v>5.81256</v>
+        <v>5.924340000000001</v>
       </c>
       <c r="N54">
-        <v>3.637439999999999</v>
+        <v>3.525659999999998</v>
       </c>
       <c r="O54">
-        <v>0.6911135999999998</v>
+        <v>0.6698753999999997</v>
       </c>
       <c r="P54">
-        <v>2.946326399999999</v>
+        <v>2.855784599999999</v>
       </c>
       <c r="Q54">
-        <v>23.2463264</v>
+        <v>23.1557846</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09540580083105832</v>
+        <v>0.09635443430021898</v>
       </c>
       <c r="T54">
-        <v>0.8364250667770431</v>
+        <v>0.8524203898944328</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.62578966926793</v>
+        <v>1.59511439248929</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08392358412110293</v>
+        <v>0.08414438384329787</v>
       </c>
       <c r="C55">
-        <v>52.17801510422446</v>
+        <v>50.79000039981074</v>
       </c>
       <c r="D55">
-        <v>117.8060151042245</v>
+        <v>117.6600003998108</v>
       </c>
       <c r="E55">
-        <v>3.626000000000005</v>
+        <v>4.868000000000009</v>
       </c>
       <c r="F55">
-        <v>65.82600000000001</v>
+        <v>67.06800000000001</v>
       </c>
       <c r="G55">
         <v>0.198</v>
@@ -5779,28 +5779,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M55">
-        <v>5.924340000000001</v>
+        <v>6.036120000000001</v>
       </c>
       <c r="N55">
-        <v>3.525659999999998</v>
+        <v>3.413879999999998</v>
       </c>
       <c r="O55">
-        <v>0.6698753999999997</v>
+        <v>0.6486371999999996</v>
       </c>
       <c r="P55">
-        <v>2.855784599999999</v>
+        <v>2.765242799999998</v>
       </c>
       <c r="Q55">
-        <v>23.1557846</v>
+        <v>23.0652428</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09635443430021898</v>
+        <v>0.09734431270282143</v>
       </c>
       <c r="T55">
-        <v>0.8524203898944328</v>
+        <v>0.8691111618430134</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.59511439248929</v>
+        <v>1.565575237072821</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08414438384329787</v>
+        <v>0.0843651835654928</v>
       </c>
       <c r="C56">
-        <v>50.79000039981074</v>
+        <v>49.40234720327339</v>
       </c>
       <c r="D56">
-        <v>117.6600003998108</v>
+        <v>117.5143472032734</v>
       </c>
       <c r="E56">
-        <v>4.868000000000009</v>
+        <v>6.109999999999999</v>
       </c>
       <c r="F56">
-        <v>67.06800000000001</v>
+        <v>68.31</v>
       </c>
       <c r="G56">
         <v>0.198</v>
@@ -5861,28 +5861,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M56">
-        <v>6.036120000000001</v>
+        <v>6.1479</v>
       </c>
       <c r="N56">
-        <v>3.413879999999998</v>
+        <v>3.302099999999999</v>
       </c>
       <c r="O56">
-        <v>0.6486371999999996</v>
+        <v>0.6273989999999999</v>
       </c>
       <c r="P56">
-        <v>2.765242799999998</v>
+        <v>2.674700999999999</v>
       </c>
       <c r="Q56">
-        <v>23.0652428</v>
+        <v>22.974701</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09734431270282143</v>
+        <v>0.09837818570109509</v>
       </c>
       <c r="T56">
-        <v>0.8691111618430134</v>
+        <v>0.8865437458781975</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.565575237072821</v>
+        <v>1.537110232762406</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0843651835654928</v>
+        <v>0.08458598328768772</v>
       </c>
       <c r="C57">
-        <v>49.40234720327339</v>
+        <v>48.01505417372319</v>
       </c>
       <c r="D57">
-        <v>117.5143472032734</v>
+        <v>117.3690541737232</v>
       </c>
       <c r="E57">
-        <v>6.109999999999999</v>
+        <v>7.352000000000004</v>
       </c>
       <c r="F57">
-        <v>68.31</v>
+        <v>69.55200000000001</v>
       </c>
       <c r="G57">
         <v>0.198</v>
@@ -5943,28 +5943,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M57">
-        <v>6.1479</v>
+        <v>6.25968</v>
       </c>
       <c r="N57">
-        <v>3.302099999999999</v>
+        <v>3.190319999999999</v>
       </c>
       <c r="O57">
-        <v>0.6273989999999999</v>
+        <v>0.6061607999999998</v>
       </c>
       <c r="P57">
-        <v>2.674700999999999</v>
+        <v>2.584159199999999</v>
       </c>
       <c r="Q57">
-        <v>22.974701</v>
+        <v>22.8841592</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09837818570109509</v>
+        <v>0.09945905292656301</v>
       </c>
       <c r="T57">
-        <v>0.8865437458781975</v>
+        <v>0.9047687200967991</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.537110232762406</v>
+        <v>1.509661835748792</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08458598328768772</v>
+        <v>0.1127327790438336</v>
       </c>
       <c r="C58">
-        <v>48.01505417372319</v>
+        <v>30.79309794707453</v>
       </c>
       <c r="D58">
-        <v>117.3690541737232</v>
+        <v>101.3890979470745</v>
       </c>
       <c r="E58">
-        <v>7.352000000000004</v>
+        <v>8.594000000000008</v>
       </c>
       <c r="F58">
-        <v>69.55200000000001</v>
+        <v>70.79400000000001</v>
       </c>
       <c r="G58">
         <v>0.198</v>
@@ -6025,45 +6025,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M58">
-        <v>6.25968</v>
+        <v>10.3925592</v>
       </c>
       <c r="N58">
-        <v>3.190319999999999</v>
+        <v>-0.9425592000000034</v>
       </c>
       <c r="O58">
-        <v>0.6061607999999998</v>
+        <v>-0.1790862480000006</v>
       </c>
       <c r="P58">
-        <v>2.584159199999999</v>
+        <v>-0.7634729520000028</v>
       </c>
       <c r="Q58">
-        <v>22.8841592</v>
+        <v>19.536527048</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09945905292656301</v>
+        <v>0.1011937227510791</v>
       </c>
       <c r="T58">
-        <v>0.9047687200967991</v>
+        <v>0.9340177454022942</v>
       </c>
       <c r="U58">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.19</v>
+        <v>0.1727678395134857</v>
       </c>
       <c r="W58">
-        <v>0.07290000000000001</v>
+        <v>0.1214376811594203</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.509661835748792</v>
+        <v>0.90930441849203</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1127327790438336</v>
+        <v>0.1137427790438336</v>
       </c>
       <c r="C59">
-        <v>30.79309794707453</v>
+        <v>29.05816363894445</v>
       </c>
       <c r="D59">
-        <v>101.3890979470745</v>
+        <v>100.8961636389445</v>
       </c>
       <c r="E59">
-        <v>8.594000000000008</v>
+        <v>9.836000000000013</v>
       </c>
       <c r="F59">
-        <v>70.79400000000001</v>
+        <v>72.03600000000002</v>
       </c>
       <c r="G59">
         <v>0.198</v>
@@ -6107,37 +6107,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M59">
-        <v>10.3925592</v>
+        <v>10.5748848</v>
       </c>
       <c r="N59">
-        <v>-0.9425592000000034</v>
+        <v>-1.124884800000004</v>
       </c>
       <c r="O59">
-        <v>-0.1790862480000006</v>
+        <v>-0.2137281120000007</v>
       </c>
       <c r="P59">
-        <v>-0.7634729520000028</v>
+        <v>-0.911156688000003</v>
       </c>
       <c r="Q59">
-        <v>19.536527048</v>
+        <v>19.388843312</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1011937227510791</v>
+        <v>0.1025126209118191</v>
       </c>
       <c r="T59">
-        <v>0.9340177454022942</v>
+        <v>0.9562562631499681</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1727678395134857</v>
+        <v>0.1697890836598049</v>
       </c>
       <c r="W59">
-        <v>0.1214376811594203</v>
+        <v>0.1218749625187407</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.90930441849203</v>
+        <v>0.8936267561042364</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1137427790438336</v>
+        <v>0.1147527790438336</v>
       </c>
       <c r="C60">
-        <v>29.05816363894446</v>
+        <v>27.32799924414952</v>
       </c>
       <c r="D60">
-        <v>100.8961636389445</v>
+        <v>100.4079992441495</v>
       </c>
       <c r="E60">
-        <v>9.835999999999999</v>
+        <v>11.07799999999999</v>
       </c>
       <c r="F60">
-        <v>72.036</v>
+        <v>73.27799999999999</v>
       </c>
       <c r="G60">
         <v>0.198</v>
@@ -6189,37 +6189,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M60">
-        <v>10.5748848</v>
+        <v>10.7572104</v>
       </c>
       <c r="N60">
-        <v>-1.124884800000002</v>
+        <v>-1.307210400000001</v>
       </c>
       <c r="O60">
-        <v>-0.2137281120000004</v>
+        <v>-0.2483699760000001</v>
       </c>
       <c r="P60">
-        <v>-0.9111566880000016</v>
+        <v>-1.058840424</v>
       </c>
       <c r="Q60">
-        <v>19.388843312</v>
+        <v>19.241159576</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.102512620911819</v>
+        <v>0.1038958555682049</v>
       </c>
       <c r="T60">
-        <v>0.9562562631499677</v>
+        <v>0.9795795866414304</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1697890836598049</v>
+        <v>0.1669113025808252</v>
       </c>
       <c r="W60">
-        <v>0.1218749625187407</v>
+        <v>0.1222974207811349</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8936267561042366</v>
+        <v>0.87848053989908</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1147527790438336</v>
+        <v>0.1157627790438336</v>
       </c>
       <c r="C61">
-        <v>27.32799924414952</v>
+        <v>25.60253586145313</v>
       </c>
       <c r="D61">
-        <v>100.4079992441495</v>
+        <v>99.92453586145314</v>
       </c>
       <c r="E61">
-        <v>11.07799999999999</v>
+        <v>12.31999999999999</v>
       </c>
       <c r="F61">
-        <v>73.27799999999999</v>
+        <v>74.52</v>
       </c>
       <c r="G61">
         <v>0.198</v>
@@ -6271,37 +6271,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M61">
-        <v>10.7572104</v>
+        <v>10.939536</v>
       </c>
       <c r="N61">
-        <v>-1.307210400000001</v>
+        <v>-1.489536000000001</v>
       </c>
       <c r="O61">
-        <v>-0.2483699760000001</v>
+        <v>-0.2830118400000002</v>
       </c>
       <c r="P61">
-        <v>-1.058840424</v>
+        <v>-1.206524160000001</v>
       </c>
       <c r="Q61">
-        <v>19.241159576</v>
+        <v>19.09347584</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1038958555682049</v>
+        <v>0.10534825195741</v>
       </c>
       <c r="T61">
-        <v>0.9795795866414304</v>
+        <v>1.004069076307466</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1669113025808252</v>
+        <v>0.1641294475378115</v>
       </c>
       <c r="W61">
-        <v>0.1222974207811349</v>
+        <v>0.1227057971014493</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.87848053989908</v>
+        <v>0.8638391975674287</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1157627790438336</v>
+        <v>0.1167727790438336</v>
       </c>
       <c r="C62">
-        <v>25.60253586145313</v>
+        <v>23.8817059102944</v>
       </c>
       <c r="D62">
-        <v>99.92453586145314</v>
+        <v>99.44570591029441</v>
       </c>
       <c r="E62">
-        <v>12.31999999999999</v>
+        <v>13.562</v>
       </c>
       <c r="F62">
-        <v>74.52</v>
+        <v>75.762</v>
       </c>
       <c r="G62">
         <v>0.198</v>
@@ -6353,37 +6353,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M62">
-        <v>10.939536</v>
+        <v>11.1218616</v>
       </c>
       <c r="N62">
-        <v>-1.489536000000001</v>
+        <v>-1.671861600000002</v>
       </c>
       <c r="O62">
-        <v>-0.2830118400000002</v>
+        <v>-0.3176537040000003</v>
       </c>
       <c r="P62">
-        <v>-1.206524160000001</v>
+        <v>-1.354207896000001</v>
       </c>
       <c r="Q62">
-        <v>19.09347584</v>
+        <v>18.945792104</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.10534825195741</v>
+        <v>0.1068751302127282</v>
       </c>
       <c r="T62">
-        <v>1.004069076307466</v>
+        <v>1.029814437238427</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1641294475378115</v>
+        <v>0.1614388008568637</v>
       </c>
       <c r="W62">
-        <v>0.1227057971014493</v>
+        <v>0.1231007840342124</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8638391975674287</v>
+        <v>0.8496778992466512</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1167727790438336</v>
+        <v>0.1177827790438336</v>
       </c>
       <c r="C63">
-        <v>23.8817059102944</v>
+        <v>22.16544309929618</v>
       </c>
       <c r="D63">
-        <v>99.44570591029441</v>
+        <v>98.9714430992962</v>
       </c>
       <c r="E63">
-        <v>13.562</v>
+        <v>14.804</v>
       </c>
       <c r="F63">
-        <v>75.762</v>
+        <v>77.004</v>
       </c>
       <c r="G63">
         <v>0.198</v>
@@ -6435,37 +6435,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M63">
-        <v>11.1218616</v>
+        <v>11.3041872</v>
       </c>
       <c r="N63">
-        <v>-1.671861600000002</v>
+        <v>-1.854187200000002</v>
       </c>
       <c r="O63">
-        <v>-0.3176537040000003</v>
+        <v>-0.3522955680000004</v>
       </c>
       <c r="P63">
-        <v>-1.354207896000001</v>
+        <v>-1.501891632000002</v>
       </c>
       <c r="Q63">
-        <v>18.945792104</v>
+        <v>18.798108368</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1068751302127282</v>
+        <v>0.1084823704814842</v>
       </c>
       <c r="T63">
-        <v>1.029814437238427</v>
+        <v>1.056914817165754</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1614388008568637</v>
+        <v>0.1588349492301401</v>
       </c>
       <c r="W63">
-        <v>0.1231007840342124</v>
+        <v>0.1234830294530154</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8496778992466512</v>
+        <v>0.8359734170007374</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1177827790438336</v>
+        <v>0.1187927790438336</v>
       </c>
       <c r="C64">
-        <v>22.16544309929618</v>
+        <v>20.45368239566997</v>
       </c>
       <c r="D64">
-        <v>98.9714430992962</v>
+        <v>98.50168239566999</v>
       </c>
       <c r="E64">
-        <v>14.804</v>
+        <v>16.04600000000001</v>
       </c>
       <c r="F64">
-        <v>77.004</v>
+        <v>78.24600000000001</v>
       </c>
       <c r="G64">
         <v>0.198</v>
@@ -6517,37 +6517,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M64">
-        <v>11.3041872</v>
+        <v>11.4865128</v>
       </c>
       <c r="N64">
-        <v>-1.854187200000002</v>
+        <v>-2.036512800000002</v>
       </c>
       <c r="O64">
-        <v>-0.3522955680000004</v>
+        <v>-0.3869374320000005</v>
       </c>
       <c r="P64">
-        <v>-1.501891632000002</v>
+        <v>-1.649575368000002</v>
       </c>
       <c r="Q64">
-        <v>18.798108368</v>
+        <v>18.650424632</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1084823704814842</v>
+        <v>0.1101764886026054</v>
       </c>
       <c r="T64">
-        <v>1.056914817165754</v>
+        <v>1.085480082494558</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1588349492301401</v>
+        <v>0.1563137595598204</v>
       </c>
       <c r="W64">
-        <v>0.1234830294530154</v>
+        <v>0.1238531400966184</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8359734170007374</v>
+        <v>0.8227039976832653</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1187927790438336</v>
+        <v>0.1198027790438336</v>
       </c>
       <c r="C65">
-        <v>20.45368239566997</v>
+        <v>18.74635999548808</v>
       </c>
       <c r="D65">
-        <v>98.50168239566999</v>
+        <v>98.03635999548808</v>
       </c>
       <c r="E65">
-        <v>16.04600000000001</v>
+        <v>17.288</v>
       </c>
       <c r="F65">
-        <v>78.24600000000001</v>
+        <v>79.488</v>
       </c>
       <c r="G65">
         <v>0.198</v>
@@ -6599,37 +6599,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M65">
-        <v>11.4865128</v>
+        <v>11.6688384</v>
       </c>
       <c r="N65">
-        <v>-2.036512800000002</v>
+        <v>-2.218838400000001</v>
       </c>
       <c r="O65">
-        <v>-0.3869374320000005</v>
+        <v>-0.4215792960000002</v>
       </c>
       <c r="P65">
-        <v>-1.649575368000002</v>
+        <v>-1.797259104000001</v>
       </c>
       <c r="Q65">
-        <v>18.650424632</v>
+        <v>18.502740896</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1101764886026054</v>
+        <v>0.1119647243971222</v>
       </c>
       <c r="T65">
-        <v>1.085480082494558</v>
+        <v>1.115632307008296</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1563137595598204</v>
+        <v>0.1538713570666982</v>
       </c>
       <c r="W65">
-        <v>0.1238531400966184</v>
+        <v>0.1242116847826087</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8227039976832653</v>
+        <v>0.8098492477194644</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1198027790438336</v>
+        <v>0.1566124926660328</v>
       </c>
       <c r="C66">
-        <v>18.74635999548808</v>
+        <v>3.104812371943297</v>
       </c>
       <c r="D66">
-        <v>98.03635999548808</v>
+        <v>83.63681237194331</v>
       </c>
       <c r="E66">
-        <v>17.288</v>
+        <v>18.53</v>
       </c>
       <c r="F66">
-        <v>79.488</v>
+        <v>80.73</v>
       </c>
       <c r="G66">
         <v>0.198</v>
@@ -6681,45 +6681,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M66">
-        <v>11.6688384</v>
+        <v>16.210584</v>
       </c>
       <c r="N66">
-        <v>-2.218838400000001</v>
+        <v>-6.760584000000001</v>
       </c>
       <c r="O66">
-        <v>-0.4215792960000002</v>
+        <v>-1.28451096</v>
       </c>
       <c r="P66">
-        <v>-1.797259104000001</v>
+        <v>-5.476073040000001</v>
       </c>
       <c r="Q66">
-        <v>18.502740896</v>
+        <v>14.82392696</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1119647243971222</v>
+        <v>0.1158543268718949</v>
       </c>
       <c r="T66">
-        <v>1.115632307008296</v>
+        <v>1.181216592619928</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1538713570666982</v>
+        <v>0.1107609694999267</v>
       </c>
       <c r="W66">
-        <v>0.1242116847826087</v>
+        <v>0.1785591973244147</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8098492477194644</v>
+        <v>0.5829524710522458</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1566124926660328</v>
+        <v>0.1581624926660328</v>
       </c>
       <c r="C67">
-        <v>3.104812371943297</v>
+        <v>1.348708804304465</v>
       </c>
       <c r="D67">
-        <v>83.63681237194331</v>
+        <v>83.12270880430448</v>
       </c>
       <c r="E67">
-        <v>18.53</v>
+        <v>19.77200000000001</v>
       </c>
       <c r="F67">
-        <v>80.73</v>
+        <v>81.97200000000001</v>
       </c>
       <c r="G67">
         <v>0.198</v>
@@ -6763,37 +6763,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M67">
-        <v>16.210584</v>
+        <v>16.4599776</v>
       </c>
       <c r="N67">
-        <v>-6.760584000000001</v>
+        <v>-7.009977600000003</v>
       </c>
       <c r="O67">
-        <v>-1.28451096</v>
+        <v>-1.331895744000001</v>
       </c>
       <c r="P67">
-        <v>-5.476073040000001</v>
+        <v>-5.678081856000002</v>
       </c>
       <c r="Q67">
-        <v>14.82392696</v>
+        <v>14.621918144</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1158543268718949</v>
+        <v>0.11791474825048</v>
       </c>
       <c r="T67">
-        <v>1.181216592619928</v>
+        <v>1.215958257108749</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1107609694999267</v>
+        <v>0.1090827729923521</v>
       </c>
       <c r="W67">
-        <v>0.1785591973244147</v>
+        <v>0.1788961791831357</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5829524710522458</v>
+        <v>0.5741198578544844</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1581624926660328</v>
+        <v>0.1597124926660328</v>
       </c>
       <c r="C68">
-        <v>1.348708804304465</v>
+        <v>-0.401113132877768</v>
       </c>
       <c r="D68">
-        <v>83.12270880430448</v>
+        <v>82.61488686712225</v>
       </c>
       <c r="E68">
-        <v>19.77200000000001</v>
+        <v>21.01400000000001</v>
       </c>
       <c r="F68">
-        <v>81.97200000000001</v>
+        <v>83.21400000000001</v>
       </c>
       <c r="G68">
         <v>0.198</v>
@@ -6845,37 +6845,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M68">
-        <v>16.4599776</v>
+        <v>16.7093712</v>
       </c>
       <c r="N68">
-        <v>-7.009977600000003</v>
+        <v>-7.259371200000004</v>
       </c>
       <c r="O68">
-        <v>-1.331895744000001</v>
+        <v>-1.379280528000001</v>
       </c>
       <c r="P68">
-        <v>-5.678081856000002</v>
+        <v>-5.880090672000003</v>
       </c>
       <c r="Q68">
-        <v>14.621918144</v>
+        <v>14.419909328</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.11791474825048</v>
+        <v>0.1201000436520097</v>
       </c>
       <c r="T68">
-        <v>1.215958257108749</v>
+        <v>1.252805477021136</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1090827729923521</v>
+        <v>0.107454671902914</v>
       </c>
       <c r="W68">
-        <v>0.1788961791831357</v>
+        <v>0.1792231018818949</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5741198578544844</v>
+        <v>0.5655509047521787</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1597124926660328</v>
+        <v>0.1612624926660328</v>
       </c>
       <c r="C69">
-        <v>-0.401113132877768</v>
+        <v>-2.144767869694334</v>
       </c>
       <c r="D69">
-        <v>82.61488686712225</v>
+        <v>82.11323213030568</v>
       </c>
       <c r="E69">
-        <v>21.01400000000001</v>
+        <v>22.256</v>
       </c>
       <c r="F69">
-        <v>83.21400000000001</v>
+        <v>84.456</v>
       </c>
       <c r="G69">
         <v>0.198</v>
@@ -6927,37 +6927,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M69">
-        <v>16.7093712</v>
+        <v>16.9587648</v>
       </c>
       <c r="N69">
-        <v>-7.259371200000004</v>
+        <v>-7.508764800000002</v>
       </c>
       <c r="O69">
-        <v>-1.379280528000001</v>
+        <v>-1.426665312</v>
       </c>
       <c r="P69">
-        <v>-5.880090672000003</v>
+        <v>-6.082099488000001</v>
       </c>
       <c r="Q69">
-        <v>14.419909328</v>
+        <v>14.217900512</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1201000436520097</v>
+        <v>0.122421920016135</v>
       </c>
       <c r="T69">
-        <v>1.252805477021136</v>
+        <v>1.291955648178046</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.107454671902914</v>
+        <v>0.1058744561396358</v>
       </c>
       <c r="W69">
-        <v>0.1792231018818949</v>
+        <v>0.1795404092071611</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5655509047521787</v>
+        <v>0.5572339796822938</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1612624926660328</v>
+        <v>0.1628124926660328</v>
       </c>
       <c r="C70">
-        <v>-2.144767869694334</v>
+        <v>-3.882367073638321</v>
       </c>
       <c r="D70">
-        <v>82.11323213030568</v>
+        <v>81.61763292636169</v>
       </c>
       <c r="E70">
-        <v>22.256</v>
+        <v>23.498</v>
       </c>
       <c r="F70">
-        <v>84.456</v>
+        <v>85.69800000000001</v>
       </c>
       <c r="G70">
         <v>0.198</v>
@@ -7009,37 +7009,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M70">
-        <v>16.9587648</v>
+        <v>17.2081584</v>
       </c>
       <c r="N70">
-        <v>-7.508764800000002</v>
+        <v>-7.758158400000003</v>
       </c>
       <c r="O70">
-        <v>-1.426665312</v>
+        <v>-1.474050096</v>
       </c>
       <c r="P70">
-        <v>-6.082099488000001</v>
+        <v>-6.284108304000002</v>
       </c>
       <c r="Q70">
-        <v>14.217900512</v>
+        <v>14.015891696</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.122421920016135</v>
+        <v>0.1248935948553652</v>
       </c>
       <c r="T70">
-        <v>1.291955648178046</v>
+        <v>1.333631636828951</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1058744561396358</v>
+        <v>0.104340043731815</v>
       </c>
       <c r="W70">
-        <v>0.1795404092071611</v>
+        <v>0.1798485192186516</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5572339796822938</v>
+        <v>0.5491581249042895</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1628124926660328</v>
+        <v>0.1643624926660328</v>
       </c>
       <c r="C71">
-        <v>-3.882367073638321</v>
+        <v>-5.614019732473679</v>
       </c>
       <c r="D71">
-        <v>81.61763292636169</v>
+        <v>81.12798026752634</v>
       </c>
       <c r="E71">
-        <v>23.498</v>
+        <v>24.74000000000001</v>
       </c>
       <c r="F71">
-        <v>85.69800000000001</v>
+        <v>86.94000000000001</v>
       </c>
       <c r="G71">
         <v>0.198</v>
@@ -7091,37 +7091,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M71">
-        <v>17.2081584</v>
+        <v>17.457552</v>
       </c>
       <c r="N71">
-        <v>-7.758158400000003</v>
+        <v>-8.007552000000004</v>
       </c>
       <c r="O71">
-        <v>-1.474050096</v>
+        <v>-1.521434880000001</v>
       </c>
       <c r="P71">
-        <v>-6.284108304000002</v>
+        <v>-6.486117120000003</v>
       </c>
       <c r="Q71">
-        <v>14.015891696</v>
+        <v>13.81388288</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1248935948553652</v>
+        <v>0.1275300480172107</v>
       </c>
       <c r="T71">
-        <v>1.333631636828951</v>
+        <v>1.378086024723249</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.104340043731815</v>
+        <v>0.1028494716785033</v>
       </c>
       <c r="W71">
-        <v>0.1798485192186516</v>
+        <v>0.1801478260869565</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5491581249042895</v>
+        <v>0.5413130088342282</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1643624926660328</v>
+        <v>0.1659124926660328</v>
       </c>
       <c r="C72">
-        <v>-5.614019732473679</v>
+        <v>-7.33983223413918</v>
       </c>
       <c r="D72">
-        <v>81.12798026752634</v>
+        <v>80.64416776586084</v>
       </c>
       <c r="E72">
-        <v>24.74000000000001</v>
+        <v>25.98200000000001</v>
       </c>
       <c r="F72">
-        <v>86.94000000000001</v>
+        <v>88.18200000000002</v>
       </c>
       <c r="G72">
         <v>0.198</v>
@@ -7173,37 +7173,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M72">
-        <v>17.457552</v>
+        <v>17.7069456</v>
       </c>
       <c r="N72">
-        <v>-8.007552000000004</v>
+        <v>-8.256945600000005</v>
       </c>
       <c r="O72">
-        <v>-1.521434880000001</v>
+        <v>-1.568819664000001</v>
       </c>
       <c r="P72">
-        <v>-6.486117120000003</v>
+        <v>-6.688125936000004</v>
       </c>
       <c r="Q72">
-        <v>13.81388288</v>
+        <v>13.611874064</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1275300480172107</v>
+        <v>0.1303483255350456</v>
       </c>
       <c r="T72">
-        <v>1.378086024723249</v>
+        <v>1.425606232472327</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1028494716785033</v>
+        <v>0.1014008875703554</v>
       </c>
       <c r="W72">
-        <v>0.1801478260869565</v>
+        <v>0.1804387017758727</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5413130088342282</v>
+        <v>0.533688881949239</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1659124926660328</v>
+        <v>0.1674624926660327</v>
       </c>
       <c r="C73">
-        <v>-7.339832234139152</v>
+        <v>-9.059908443809903</v>
       </c>
       <c r="D73">
-        <v>80.64416776586086</v>
+        <v>80.1660915561901</v>
       </c>
       <c r="E73">
-        <v>25.982</v>
+        <v>27.22399999999999</v>
       </c>
       <c r="F73">
-        <v>88.182</v>
+        <v>89.42399999999999</v>
       </c>
       <c r="G73">
         <v>0.198</v>
@@ -7255,37 +7255,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M73">
-        <v>17.7069456</v>
+        <v>17.9563392</v>
       </c>
       <c r="N73">
-        <v>-8.256945600000002</v>
+        <v>-8.506339199999999</v>
       </c>
       <c r="O73">
-        <v>-1.568819664</v>
+        <v>-1.616204448</v>
       </c>
       <c r="P73">
-        <v>-6.688125936000001</v>
+        <v>-6.890134752</v>
       </c>
       <c r="Q73">
-        <v>13.611874064</v>
+        <v>13.409865248</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1303483255350455</v>
+        <v>0.1333679085898686</v>
       </c>
       <c r="T73">
-        <v>1.425606232472326</v>
+        <v>1.476520740774909</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1014008875703554</v>
+        <v>0.09999254190965606</v>
       </c>
       <c r="W73">
-        <v>0.1804387017758726</v>
+        <v>0.1807214975845411</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5336888819492391</v>
+        <v>0.5262765363666109</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1674624926660327</v>
+        <v>0.1690124926660327</v>
       </c>
       <c r="C74">
-        <v>-9.059908443809903</v>
+        <v>-10.77434977823432</v>
       </c>
       <c r="D74">
-        <v>80.1660915561901</v>
+        <v>79.69365022176568</v>
       </c>
       <c r="E74">
-        <v>27.22399999999999</v>
+        <v>28.46599999999999</v>
       </c>
       <c r="F74">
-        <v>89.42399999999999</v>
+        <v>90.666</v>
       </c>
       <c r="G74">
         <v>0.198</v>
@@ -7337,37 +7337,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M74">
-        <v>17.9563392</v>
+        <v>18.2057328</v>
       </c>
       <c r="N74">
-        <v>-8.506339199999999</v>
+        <v>-8.755732800000001</v>
       </c>
       <c r="O74">
-        <v>-1.616204448</v>
+        <v>-1.663589232</v>
       </c>
       <c r="P74">
-        <v>-6.890134752</v>
+        <v>-7.092143568000001</v>
       </c>
       <c r="Q74">
-        <v>13.409865248</v>
+        <v>13.207856432</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1333679085898686</v>
+        <v>0.1366111644635674</v>
       </c>
       <c r="T74">
-        <v>1.476520740774909</v>
+        <v>1.531206694136943</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.09999254190965606</v>
+        <v>0.09862278106157858</v>
       </c>
       <c r="W74">
-        <v>0.1807214975845411</v>
+        <v>0.180996545562835</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5262765363666109</v>
+        <v>0.5190672687451504</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1690124926660327</v>
+        <v>0.1705624926660328</v>
       </c>
       <c r="C75">
-        <v>-10.77434977823432</v>
+        <v>-12.48325527745762</v>
       </c>
       <c r="D75">
-        <v>79.69365022176568</v>
+        <v>79.22674472254239</v>
       </c>
       <c r="E75">
-        <v>28.46599999999999</v>
+        <v>29.708</v>
       </c>
       <c r="F75">
-        <v>90.666</v>
+        <v>91.908</v>
       </c>
       <c r="G75">
         <v>0.198</v>
@@ -7419,37 +7419,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M75">
-        <v>18.2057328</v>
+        <v>18.4551264</v>
       </c>
       <c r="N75">
-        <v>-8.755732800000001</v>
+        <v>-9.005126400000002</v>
       </c>
       <c r="O75">
-        <v>-1.663589232</v>
+        <v>-1.710974016</v>
       </c>
       <c r="P75">
-        <v>-7.092143568000001</v>
+        <v>-7.294152384000001</v>
       </c>
       <c r="Q75">
-        <v>13.207856432</v>
+        <v>13.005847616</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1366111644635674</v>
+        <v>0.14010390155832</v>
       </c>
       <c r="T75">
-        <v>1.531206694136943</v>
+        <v>1.590099259296057</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.09862278106157858</v>
+        <v>0.09729004077696263</v>
       </c>
       <c r="W75">
-        <v>0.180996545562835</v>
+        <v>0.1812641598119859</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5190672687451504</v>
+        <v>0.5120528461945402</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1705624926660328</v>
+        <v>0.1721124926660328</v>
       </c>
       <c r="C76">
-        <v>-12.48325527745762</v>
+        <v>-14.18672167403881</v>
       </c>
       <c r="D76">
-        <v>79.22674472254239</v>
+        <v>78.76527832596121</v>
       </c>
       <c r="E76">
-        <v>29.708</v>
+        <v>30.95</v>
       </c>
       <c r="F76">
-        <v>91.908</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="G76">
         <v>0.198</v>
@@ -7501,37 +7501,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M76">
-        <v>18.4551264</v>
+        <v>18.70452</v>
       </c>
       <c r="N76">
-        <v>-9.005126400000002</v>
+        <v>-9.254520000000003</v>
       </c>
       <c r="O76">
-        <v>-1.710974016</v>
+        <v>-1.758358800000001</v>
       </c>
       <c r="P76">
-        <v>-7.294152384000001</v>
+        <v>-7.496161200000002</v>
       </c>
       <c r="Q76">
-        <v>13.005847616</v>
+        <v>12.8038388</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.14010390155832</v>
+        <v>0.1438760576206528</v>
       </c>
       <c r="T76">
-        <v>1.590099259296057</v>
+        <v>1.653703229667899</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.09729004077696263</v>
+        <v>0.09599284023326982</v>
       </c>
       <c r="W76">
-        <v>0.1812641598119859</v>
+        <v>0.1815246376811594</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5120528461945402</v>
+        <v>0.5052254749119462</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1721124926660328</v>
+        <v>0.2005448355641935</v>
       </c>
       <c r="C77">
-        <v>-14.18672167403881</v>
+        <v>-23.0319442689291</v>
       </c>
       <c r="D77">
-        <v>78.76527832596121</v>
+        <v>71.16205573107092</v>
       </c>
       <c r="E77">
-        <v>30.95</v>
+        <v>32.19200000000001</v>
       </c>
       <c r="F77">
-        <v>93.15000000000001</v>
+        <v>94.39200000000001</v>
       </c>
       <c r="G77">
         <v>0.198</v>
@@ -7583,45 +7583,45 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M77">
-        <v>18.70452</v>
+        <v>22.2576336</v>
       </c>
       <c r="N77">
-        <v>-9.254520000000003</v>
+        <v>-12.8076336</v>
       </c>
       <c r="O77">
-        <v>-1.758358800000001</v>
+        <v>-2.433450384</v>
       </c>
       <c r="P77">
-        <v>-7.496161200000002</v>
+        <v>-10.374183216</v>
       </c>
       <c r="Q77">
-        <v>12.8038388</v>
+        <v>9.925816783999998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1438760576206528</v>
+        <v>0.1491389887638495</v>
       </c>
       <c r="T77">
-        <v>1.653703229667899</v>
+        <v>1.742443809582801</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09599284023326982</v>
+        <v>0.08066895305527896</v>
       </c>
       <c r="W77">
-        <v>0.1815246376811594</v>
+        <v>0.2167782608695652</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5052254749119462</v>
+        <v>0.4245734371330472</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2005448355641935</v>
+        <v>0.2024448355641935</v>
       </c>
       <c r="C78">
-        <v>-23.0319442689291</v>
+        <v>-24.73004402979934</v>
       </c>
       <c r="D78">
-        <v>71.16205573107092</v>
+        <v>70.70595597020066</v>
       </c>
       <c r="E78">
-        <v>32.19200000000001</v>
+        <v>33.434</v>
       </c>
       <c r="F78">
-        <v>94.39200000000001</v>
+        <v>95.634</v>
       </c>
       <c r="G78">
         <v>0.198</v>
@@ -7665,37 +7665,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M78">
-        <v>22.2576336</v>
+        <v>22.5504972</v>
       </c>
       <c r="N78">
-        <v>-12.8076336</v>
+        <v>-13.1004972</v>
       </c>
       <c r="O78">
-        <v>-2.433450384</v>
+        <v>-2.489094468000001</v>
       </c>
       <c r="P78">
-        <v>-10.374183216</v>
+        <v>-10.611402732</v>
       </c>
       <c r="Q78">
-        <v>9.925816783999998</v>
+        <v>9.688597267999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1491389887638495</v>
+        <v>0.1536319882753212</v>
       </c>
       <c r="T78">
-        <v>1.742443809582801</v>
+        <v>1.818202236086401</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08066895305527896</v>
+        <v>0.07962130431430131</v>
       </c>
       <c r="W78">
-        <v>0.2167782608695652</v>
+        <v>0.2170252964426878</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4245734371330472</v>
+        <v>0.4190594963910595</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2024448355641935</v>
+        <v>0.2043448355641934</v>
       </c>
       <c r="C79">
-        <v>-24.73004402979934</v>
+        <v>-26.42233445390471</v>
       </c>
       <c r="D79">
-        <v>70.70595597020066</v>
+        <v>70.2556655460953</v>
       </c>
       <c r="E79">
-        <v>33.434</v>
+        <v>34.676</v>
       </c>
       <c r="F79">
-        <v>95.634</v>
+        <v>96.876</v>
       </c>
       <c r="G79">
         <v>0.198</v>
@@ -7747,37 +7747,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M79">
-        <v>22.5504972</v>
+        <v>22.8433608</v>
       </c>
       <c r="N79">
-        <v>-13.1004972</v>
+        <v>-13.3933608</v>
       </c>
       <c r="O79">
-        <v>-2.489094468000001</v>
+        <v>-2.544738552000001</v>
       </c>
       <c r="P79">
-        <v>-10.611402732</v>
+        <v>-10.848622248</v>
       </c>
       <c r="Q79">
-        <v>9.688597267999999</v>
+        <v>9.451377751999997</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1536319882753212</v>
+        <v>0.1585334422878358</v>
       </c>
       <c r="T79">
-        <v>1.818202236086401</v>
+        <v>1.900847792272147</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07962130431430131</v>
+        <v>0.07860051836155386</v>
       </c>
       <c r="W79">
-        <v>0.2170252964426878</v>
+        <v>0.2172659977703456</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4190594963910595</v>
+        <v>0.4136869387450203</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2043448355641934</v>
+        <v>0.2062448355641935</v>
       </c>
       <c r="C80">
-        <v>-26.42233445390471</v>
+        <v>-28.10892582904908</v>
       </c>
       <c r="D80">
-        <v>70.2556655460953</v>
+        <v>69.81107417095093</v>
       </c>
       <c r="E80">
-        <v>34.676</v>
+        <v>35.91800000000001</v>
       </c>
       <c r="F80">
-        <v>96.876</v>
+        <v>98.11800000000001</v>
       </c>
       <c r="G80">
         <v>0.198</v>
@@ -7829,37 +7829,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M80">
-        <v>22.8433608</v>
+        <v>23.1362244</v>
       </c>
       <c r="N80">
-        <v>-13.3933608</v>
+        <v>-13.6862244</v>
       </c>
       <c r="O80">
-        <v>-2.544738552000001</v>
+        <v>-2.600382636000001</v>
       </c>
       <c r="P80">
-        <v>-10.848622248</v>
+        <v>-11.085841764</v>
       </c>
       <c r="Q80">
-        <v>9.451377751999997</v>
+        <v>9.214158235999998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1585334422878358</v>
+        <v>0.1639017014443994</v>
       </c>
       <c r="T80">
-        <v>1.900847792272147</v>
+        <v>1.991364353808916</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07860051836155386</v>
+        <v>0.07760557509115444</v>
       </c>
       <c r="W80">
-        <v>0.2172659977703456</v>
+        <v>0.2175006053935058</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4136869387450203</v>
+        <v>0.4084503952166023</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2062448355641935</v>
+        <v>0.2081448355641935</v>
       </c>
       <c r="C81">
-        <v>-28.10892582904908</v>
+        <v>-29.78992566890179</v>
       </c>
       <c r="D81">
-        <v>69.81107417095093</v>
+        <v>69.37207433109823</v>
       </c>
       <c r="E81">
-        <v>35.91800000000001</v>
+        <v>37.16000000000001</v>
       </c>
       <c r="F81">
-        <v>98.11800000000001</v>
+        <v>99.36000000000001</v>
       </c>
       <c r="G81">
         <v>0.198</v>
@@ -7911,37 +7911,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M81">
-        <v>23.1362244</v>
+        <v>23.429088</v>
       </c>
       <c r="N81">
-        <v>-13.6862244</v>
+        <v>-13.979088</v>
       </c>
       <c r="O81">
-        <v>-2.600382636000001</v>
+        <v>-2.656026720000001</v>
       </c>
       <c r="P81">
-        <v>-11.085841764</v>
+        <v>-11.32306128</v>
       </c>
       <c r="Q81">
-        <v>9.214158235999998</v>
+        <v>8.976938719999996</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1639017014443994</v>
+        <v>0.1698067865166194</v>
       </c>
       <c r="T81">
-        <v>1.991364353808916</v>
+        <v>2.090932571499362</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07760557509115444</v>
+        <v>0.07663550540251501</v>
       </c>
       <c r="W81">
-        <v>0.2175006053935058</v>
+        <v>0.217729347826087</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4084503952166023</v>
+        <v>0.4033447652763947</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2081448355641935</v>
+        <v>0.2100448355641935</v>
       </c>
       <c r="C82">
-        <v>-29.78992566890179</v>
+        <v>-31.46543879967683</v>
       </c>
       <c r="D82">
-        <v>69.37207433109823</v>
+        <v>68.93856120032318</v>
       </c>
       <c r="E82">
-        <v>37.16000000000001</v>
+        <v>38.402</v>
       </c>
       <c r="F82">
-        <v>99.36000000000001</v>
+        <v>100.602</v>
       </c>
       <c r="G82">
         <v>0.198</v>
@@ -7993,37 +7993,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M82">
-        <v>23.429088</v>
+        <v>23.7219516</v>
       </c>
       <c r="N82">
-        <v>-13.979088</v>
+        <v>-14.2719516</v>
       </c>
       <c r="O82">
-        <v>-2.656026720000001</v>
+        <v>-2.711670804</v>
       </c>
       <c r="P82">
-        <v>-11.32306128</v>
+        <v>-11.560280796</v>
       </c>
       <c r="Q82">
-        <v>8.976938719999996</v>
+        <v>8.739719204</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1698067865166194</v>
+        <v>0.1763334594911783</v>
       </c>
       <c r="T82">
-        <v>2.090932571499362</v>
+        <v>2.200981654209854</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07663550540251501</v>
+        <v>0.07568938805186669</v>
       </c>
       <c r="W82">
-        <v>0.217729347826087</v>
+        <v>0.2179524422973698</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4033447652763947</v>
+        <v>0.3983652002729826</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2100448355641935</v>
+        <v>0.2119448355641935</v>
       </c>
       <c r="C83">
-        <v>-31.46543879967683</v>
+        <v>-33.13556744358233</v>
       </c>
       <c r="D83">
-        <v>68.93856120032318</v>
+        <v>68.51043255641768</v>
       </c>
       <c r="E83">
-        <v>38.402</v>
+        <v>39.64400000000001</v>
       </c>
       <c r="F83">
-        <v>100.602</v>
+        <v>101.844</v>
       </c>
       <c r="G83">
         <v>0.198</v>
@@ -8075,37 +8075,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M83">
-        <v>23.7219516</v>
+        <v>24.0148152</v>
       </c>
       <c r="N83">
-        <v>-14.2719516</v>
+        <v>-14.56481520000001</v>
       </c>
       <c r="O83">
-        <v>-2.711670804</v>
+        <v>-2.767314888000001</v>
       </c>
       <c r="P83">
-        <v>-11.560280796</v>
+        <v>-11.797500312</v>
       </c>
       <c r="Q83">
-        <v>8.739719204</v>
+        <v>8.502499687999997</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1763334594911783</v>
+        <v>0.1835853183517994</v>
       </c>
       <c r="T83">
-        <v>2.200981654209854</v>
+        <v>2.323258412777069</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07568938805186669</v>
+        <v>0.07476634673416098</v>
       </c>
       <c r="W83">
-        <v>0.2179524422973698</v>
+        <v>0.2181700954400849</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3983652002729826</v>
+        <v>0.3935070880745315</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2119448355641935</v>
+        <v>0.2138448355641935</v>
       </c>
       <c r="C84">
-        <v>-33.13556744358233</v>
+        <v>-34.80041129917967</v>
       </c>
       <c r="D84">
-        <v>68.51043255641768</v>
+        <v>68.08758870082035</v>
       </c>
       <c r="E84">
-        <v>39.64400000000001</v>
+        <v>40.88600000000001</v>
       </c>
       <c r="F84">
-        <v>101.844</v>
+        <v>103.086</v>
       </c>
       <c r="G84">
         <v>0.198</v>
@@ -8157,37 +8157,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M84">
-        <v>24.0148152</v>
+        <v>24.30767880000001</v>
       </c>
       <c r="N84">
-        <v>-14.56481520000001</v>
+        <v>-14.85767880000001</v>
       </c>
       <c r="O84">
-        <v>-2.767314888000001</v>
+        <v>-2.822958972000001</v>
       </c>
       <c r="P84">
-        <v>-11.797500312</v>
+        <v>-12.034719828</v>
       </c>
       <c r="Q84">
-        <v>8.502499687999997</v>
+        <v>8.265280171999997</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1835853183517994</v>
+        <v>0.1916903370783758</v>
       </c>
       <c r="T84">
-        <v>2.323258412777069</v>
+        <v>2.459920672352191</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07476634673416098</v>
+        <v>0.07386554737591808</v>
       </c>
       <c r="W84">
-        <v>0.2181700954400849</v>
+        <v>0.2183825039287585</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3935070880745315</v>
+        <v>0.3887660388206214</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2138448355641935</v>
+        <v>0.2157448355641935</v>
       </c>
       <c r="C85">
-        <v>-34.80041129917967</v>
+        <v>-36.46006761878503</v>
       </c>
       <c r="D85">
-        <v>68.08758870082035</v>
+        <v>67.66993238121499</v>
       </c>
       <c r="E85">
-        <v>40.88600000000001</v>
+        <v>42.12800000000001</v>
       </c>
       <c r="F85">
-        <v>103.086</v>
+        <v>104.328</v>
       </c>
       <c r="G85">
         <v>0.198</v>
@@ -8239,37 +8239,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M85">
-        <v>24.30767880000001</v>
+        <v>24.60054240000001</v>
       </c>
       <c r="N85">
-        <v>-14.85767880000001</v>
+        <v>-15.15054240000001</v>
       </c>
       <c r="O85">
-        <v>-2.822958972000001</v>
+        <v>-2.878603056000001</v>
       </c>
       <c r="P85">
-        <v>-12.034719828</v>
+        <v>-12.27193934400001</v>
       </c>
       <c r="Q85">
-        <v>8.265280171999997</v>
+        <v>8.028060655999996</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1916903370783758</v>
+        <v>0.2008084831457743</v>
       </c>
       <c r="T85">
-        <v>2.459920672352191</v>
+        <v>2.613665714374203</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07386554737591808</v>
+        <v>0.07298619562144286</v>
       </c>
       <c r="W85">
-        <v>0.2183825039287585</v>
+        <v>0.2185898550724638</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3887660388206214</v>
+        <v>0.3841378716918046</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2157448355641935</v>
+        <v>0.2176448355641935</v>
       </c>
       <c r="C86">
-        <v>-36.460067618785</v>
+        <v>-38.11463128303954</v>
       </c>
       <c r="D86">
-        <v>67.66993238121501</v>
+        <v>67.25736871696046</v>
       </c>
       <c r="E86">
-        <v>42.128</v>
+        <v>43.36999999999999</v>
       </c>
       <c r="F86">
-        <v>104.328</v>
+        <v>105.57</v>
       </c>
       <c r="G86">
         <v>0.198</v>
@@ -8321,37 +8321,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M86">
-        <v>24.6005424</v>
+        <v>24.893406</v>
       </c>
       <c r="N86">
-        <v>-15.1505424</v>
+        <v>-15.443406</v>
       </c>
       <c r="O86">
-        <v>-2.878603056000001</v>
+        <v>-2.93424714</v>
       </c>
       <c r="P86">
-        <v>-12.271939344</v>
+        <v>-12.50915886</v>
       </c>
       <c r="Q86">
-        <v>8.028060655999999</v>
+        <v>7.790841140000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2008084831457742</v>
+        <v>0.2111423820221592</v>
       </c>
       <c r="T86">
-        <v>2.613665714374201</v>
+        <v>2.787910095332482</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07298619562144287</v>
+        <v>0.07212753449648472</v>
       </c>
       <c r="W86">
-        <v>0.2185898550724638</v>
+        <v>0.2187923273657289</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3841378716918046</v>
+        <v>0.3796186026130776</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2176448355641935</v>
+        <v>0.2195448355641935</v>
       </c>
       <c r="C87">
-        <v>-38.11463128303954</v>
+        <v>-39.76419487276833</v>
       </c>
       <c r="D87">
-        <v>67.25736871696046</v>
+        <v>66.84980512723168</v>
       </c>
       <c r="E87">
-        <v>43.36999999999999</v>
+        <v>44.61199999999999</v>
       </c>
       <c r="F87">
-        <v>105.57</v>
+        <v>106.812</v>
       </c>
       <c r="G87">
         <v>0.198</v>
@@ -8403,37 +8403,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M87">
-        <v>24.893406</v>
+        <v>25.1862696</v>
       </c>
       <c r="N87">
-        <v>-15.443406</v>
+        <v>-15.7362696</v>
       </c>
       <c r="O87">
-        <v>-2.93424714</v>
+        <v>-2.989891224</v>
       </c>
       <c r="P87">
-        <v>-12.50915886</v>
+        <v>-12.746378376</v>
       </c>
       <c r="Q87">
-        <v>7.790841140000001</v>
+        <v>7.553621624000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2111423820221592</v>
+        <v>0.2229525521665991</v>
       </c>
       <c r="T87">
-        <v>2.787910095332482</v>
+        <v>2.987046530713373</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07212753449648472</v>
+        <v>0.07128884223489769</v>
       </c>
       <c r="W87">
-        <v>0.2187923273657289</v>
+        <v>0.2189900910010111</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3796186026130776</v>
+        <v>0.3752044328152511</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2195448355641935</v>
+        <v>0.2214448355641934</v>
       </c>
       <c r="C88">
-        <v>-39.76419487276833</v>
+        <v>-41.40884873824233</v>
       </c>
       <c r="D88">
-        <v>66.84980512723168</v>
+        <v>66.44715126175768</v>
       </c>
       <c r="E88">
-        <v>44.61199999999999</v>
+        <v>45.854</v>
       </c>
       <c r="F88">
-        <v>106.812</v>
+        <v>108.054</v>
       </c>
       <c r="G88">
         <v>0.198</v>
@@ -8485,37 +8485,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M88">
-        <v>25.1862696</v>
+        <v>25.4791332</v>
       </c>
       <c r="N88">
-        <v>-15.7362696</v>
+        <v>-16.0291332</v>
       </c>
       <c r="O88">
-        <v>-2.989891224</v>
+        <v>-3.045535308000001</v>
       </c>
       <c r="P88">
-        <v>-12.746378376</v>
+        <v>-12.983597892</v>
       </c>
       <c r="Q88">
-        <v>7.553621624000002</v>
+        <v>7.316402107999998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2229525521665991</v>
+        <v>0.2365796715640298</v>
       </c>
       <c r="T88">
-        <v>2.987046530713373</v>
+        <v>3.216819340768248</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07128884223489769</v>
+        <v>0.07046943025518622</v>
       </c>
       <c r="W88">
-        <v>0.2189900910010111</v>
+        <v>0.2191833083458271</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3752044328152511</v>
+        <v>0.3708917381851906</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2214448355641934</v>
+        <v>0.2233448355641935</v>
       </c>
       <c r="C89">
-        <v>-41.40884873824233</v>
+        <v>-43.04868106595221</v>
       </c>
       <c r="D89">
-        <v>66.44715126175768</v>
+        <v>66.0493189340478</v>
       </c>
       <c r="E89">
-        <v>45.854</v>
+        <v>47.096</v>
       </c>
       <c r="F89">
-        <v>108.054</v>
+        <v>109.296</v>
       </c>
       <c r="G89">
         <v>0.198</v>
@@ -8567,37 +8567,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M89">
-        <v>25.4791332</v>
+        <v>25.7719968</v>
       </c>
       <c r="N89">
-        <v>-16.0291332</v>
+        <v>-16.3219968</v>
       </c>
       <c r="O89">
-        <v>-3.045535308000001</v>
+        <v>-3.101179392000001</v>
       </c>
       <c r="P89">
-        <v>-12.983597892</v>
+        <v>-13.220817408</v>
       </c>
       <c r="Q89">
-        <v>7.316402107999998</v>
+        <v>7.079182591999997</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2365796715640298</v>
+        <v>0.252477977527699</v>
       </c>
       <c r="T89">
-        <v>3.216819340768248</v>
+        <v>3.484887619165602</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07046943025518622</v>
+        <v>0.06966864127501365</v>
       </c>
       <c r="W89">
-        <v>0.2191833083458271</v>
+        <v>0.2193721343873518</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3708917381851906</v>
+        <v>0.3666770593421771</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2233448355641935</v>
+        <v>0.2252448355641934</v>
       </c>
       <c r="C90">
-        <v>-43.04868106595221</v>
+        <v>-44.68377794299784</v>
       </c>
       <c r="D90">
-        <v>66.0493189340478</v>
+        <v>65.65622205700218</v>
       </c>
       <c r="E90">
-        <v>47.096</v>
+        <v>48.33800000000001</v>
       </c>
       <c r="F90">
-        <v>109.296</v>
+        <v>110.538</v>
       </c>
       <c r="G90">
         <v>0.198</v>
@@ -8649,37 +8649,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M90">
-        <v>25.7719968</v>
+        <v>26.0648604</v>
       </c>
       <c r="N90">
-        <v>-16.3219968</v>
+        <v>-16.6148604</v>
       </c>
       <c r="O90">
-        <v>-3.101179392000001</v>
+        <v>-3.156823476000001</v>
       </c>
       <c r="P90">
-        <v>-13.220817408</v>
+        <v>-13.458036924</v>
       </c>
       <c r="Q90">
-        <v>7.079182591999997</v>
+        <v>6.841963075999997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.252477977527699</v>
+        <v>0.2712668845756717</v>
       </c>
       <c r="T90">
-        <v>3.484887619165602</v>
+        <v>3.801695584544294</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06966864127501365</v>
+        <v>0.06888584755282248</v>
       </c>
       <c r="W90">
-        <v>0.2193721343873518</v>
+        <v>0.2195567171470445</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3666770593421771</v>
+        <v>0.3625570923832762</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2252448355641934</v>
+        <v>0.2271448355641935</v>
       </c>
       <c r="C91">
-        <v>-44.68377794299784</v>
+        <v>-46.31422341919182</v>
       </c>
       <c r="D91">
-        <v>65.65622205700218</v>
+        <v>65.26777658080819</v>
       </c>
       <c r="E91">
-        <v>48.33800000000001</v>
+        <v>49.58</v>
       </c>
       <c r="F91">
-        <v>110.538</v>
+        <v>111.78</v>
       </c>
       <c r="G91">
         <v>0.198</v>
@@ -8731,37 +8731,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M91">
-        <v>26.0648604</v>
+        <v>26.357724</v>
       </c>
       <c r="N91">
-        <v>-16.6148604</v>
+        <v>-16.907724</v>
       </c>
       <c r="O91">
-        <v>-3.156823476000001</v>
+        <v>-3.21246756</v>
       </c>
       <c r="P91">
-        <v>-13.458036924</v>
+        <v>-13.69525644</v>
       </c>
       <c r="Q91">
-        <v>6.841963075999997</v>
+        <v>6.604743559999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2712668845756717</v>
+        <v>0.2938135730332388</v>
       </c>
       <c r="T91">
-        <v>3.801695584544294</v>
+        <v>4.181865142998723</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06888584755282248</v>
+        <v>0.06812044924668002</v>
       </c>
       <c r="W91">
-        <v>0.2195567171470445</v>
+        <v>0.2197371980676329</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3625570923832762</v>
+        <v>0.3585286802456843</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2271448355641935</v>
+        <v>0.2290448355641935</v>
       </c>
       <c r="C92">
-        <v>-46.31422341919182</v>
+        <v>-47.94009956697187</v>
       </c>
       <c r="D92">
-        <v>65.26777658080819</v>
+        <v>64.88390043302815</v>
       </c>
       <c r="E92">
-        <v>49.58</v>
+        <v>50.822</v>
       </c>
       <c r="F92">
-        <v>111.78</v>
+        <v>113.022</v>
       </c>
       <c r="G92">
         <v>0.198</v>
@@ -8813,37 +8813,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M92">
-        <v>26.357724</v>
+        <v>26.6505876</v>
       </c>
       <c r="N92">
-        <v>-16.907724</v>
+        <v>-17.2005876</v>
       </c>
       <c r="O92">
-        <v>-3.21246756</v>
+        <v>-3.268111644000001</v>
       </c>
       <c r="P92">
-        <v>-13.69525644</v>
+        <v>-13.932475956</v>
       </c>
       <c r="Q92">
-        <v>6.604743559999999</v>
+        <v>6.367524044</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2938135730332388</v>
+        <v>0.3213706367035987</v>
       </c>
       <c r="T92">
-        <v>4.181865142998723</v>
+        <v>4.646516825554137</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06812044924668002</v>
+        <v>0.06737187288133188</v>
       </c>
       <c r="W92">
-        <v>0.2197371980676329</v>
+        <v>0.219913712374582</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3585286802456843</v>
+        <v>0.3545888046385889</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2290448355641935</v>
+        <v>0.2309448355641935</v>
       </c>
       <c r="C93">
-        <v>-47.94009956697187</v>
+        <v>-49.5614865392107</v>
       </c>
       <c r="D93">
-        <v>64.88390043302815</v>
+        <v>64.50451346078931</v>
       </c>
       <c r="E93">
-        <v>50.822</v>
+        <v>52.06400000000001</v>
       </c>
       <c r="F93">
-        <v>113.022</v>
+        <v>114.264</v>
       </c>
       <c r="G93">
         <v>0.198</v>
@@ -8895,37 +8895,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M93">
-        <v>26.6505876</v>
+        <v>26.9434512</v>
       </c>
       <c r="N93">
-        <v>-17.2005876</v>
+        <v>-17.4934512</v>
       </c>
       <c r="O93">
-        <v>-3.268111644000001</v>
+        <v>-3.323755728000001</v>
       </c>
       <c r="P93">
-        <v>-13.932475956</v>
+        <v>-14.169695472</v>
       </c>
       <c r="Q93">
-        <v>6.367524044</v>
+        <v>6.130304527999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3213706367035987</v>
+        <v>0.3558169662915487</v>
       </c>
       <c r="T93">
-        <v>4.646516825554137</v>
+        <v>5.227331428748406</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06737187288133188</v>
+        <v>0.06663956991523044</v>
       </c>
       <c r="W93">
-        <v>0.219913712374582</v>
+        <v>0.2200863894139887</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3545888046385889</v>
+        <v>0.3507345785012129</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2309448355641935</v>
+        <v>0.2328448355641935</v>
       </c>
       <c r="C94">
-        <v>-49.5614865392107</v>
+        <v>-51.1784626250101</v>
       </c>
       <c r="D94">
-        <v>64.50451346078931</v>
+        <v>64.12953737498992</v>
       </c>
       <c r="E94">
-        <v>52.06400000000001</v>
+        <v>53.30600000000001</v>
       </c>
       <c r="F94">
-        <v>114.264</v>
+        <v>115.506</v>
       </c>
       <c r="G94">
         <v>0.198</v>
@@ -8977,37 +8977,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M94">
-        <v>26.9434512</v>
+        <v>27.23631480000001</v>
       </c>
       <c r="N94">
-        <v>-17.4934512</v>
+        <v>-17.78631480000001</v>
       </c>
       <c r="O94">
-        <v>-3.323755728000001</v>
+        <v>-3.379399812000001</v>
       </c>
       <c r="P94">
-        <v>-14.169695472</v>
+        <v>-14.40691498800001</v>
       </c>
       <c r="Q94">
-        <v>6.130304527999998</v>
+        <v>5.893085011999995</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3558169662915487</v>
+        <v>0.4001051043331986</v>
       </c>
       <c r="T94">
-        <v>5.227331428748406</v>
+        <v>5.974093061426752</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06663956991523044</v>
+        <v>0.06592301540001291</v>
       </c>
       <c r="W94">
-        <v>0.2200863894139887</v>
+        <v>0.220255352968677</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3507345785012129</v>
+        <v>0.3469632389474363</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2328448355641935</v>
+        <v>0.2347448355641935</v>
       </c>
       <c r="C95">
-        <v>-51.1784626250101</v>
+        <v>-52.79110430355983</v>
       </c>
       <c r="D95">
-        <v>64.12953737498992</v>
+        <v>63.75889569644017</v>
       </c>
       <c r="E95">
-        <v>53.30600000000001</v>
+        <v>54.548</v>
       </c>
       <c r="F95">
-        <v>115.506</v>
+        <v>116.748</v>
       </c>
       <c r="G95">
         <v>0.198</v>
@@ -9059,37 +9059,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M95">
-        <v>27.23631480000001</v>
+        <v>27.5291784</v>
       </c>
       <c r="N95">
-        <v>-17.78631480000001</v>
+        <v>-18.0791784</v>
       </c>
       <c r="O95">
-        <v>-3.379399812000001</v>
+        <v>-3.435043896000001</v>
       </c>
       <c r="P95">
-        <v>-14.40691498800001</v>
+        <v>-14.644134504</v>
       </c>
       <c r="Q95">
-        <v>5.893085011999995</v>
+        <v>5.655865495999997</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4001051043331986</v>
+        <v>0.4591559550553984</v>
       </c>
       <c r="T95">
-        <v>5.974093061426752</v>
+        <v>6.969775238331211</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06592301540001291</v>
+        <v>0.0652217067255447</v>
       </c>
       <c r="W95">
-        <v>0.220255352968677</v>
+        <v>0.2204207215541166</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3469632389474363</v>
+        <v>0.3432721406607615</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2347448355641935</v>
+        <v>0.2366448355641935</v>
       </c>
       <c r="C96">
-        <v>-52.79110430355983</v>
+        <v>-54.39948629613992</v>
       </c>
       <c r="D96">
-        <v>63.75889569644017</v>
+        <v>63.39251370386009</v>
       </c>
       <c r="E96">
-        <v>54.548</v>
+        <v>55.79000000000001</v>
       </c>
       <c r="F96">
-        <v>116.748</v>
+        <v>117.99</v>
       </c>
       <c r="G96">
         <v>0.198</v>
@@ -9141,37 +9141,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M96">
-        <v>27.5291784</v>
+        <v>27.822042</v>
       </c>
       <c r="N96">
-        <v>-18.0791784</v>
+        <v>-18.372042</v>
       </c>
       <c r="O96">
-        <v>-3.435043896000001</v>
+        <v>-3.490687980000001</v>
       </c>
       <c r="P96">
-        <v>-14.644134504</v>
+        <v>-14.88135402</v>
       </c>
       <c r="Q96">
-        <v>5.655865495999997</v>
+        <v>5.418645979999997</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4591559550553984</v>
+        <v>0.5418271460664783</v>
       </c>
       <c r="T96">
-        <v>6.969775238331211</v>
+        <v>8.363730285997457</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0652217067255447</v>
+        <v>0.06453516244422317</v>
       </c>
       <c r="W96">
-        <v>0.2204207215541166</v>
+        <v>0.2205826086956522</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3432721406607615</v>
+        <v>0.3396587497064377</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2366448355641935</v>
+        <v>0.2385448355641935</v>
       </c>
       <c r="C97">
-        <v>-54.39948629613992</v>
+        <v>-56.00368161633979</v>
       </c>
       <c r="D97">
-        <v>63.39251370386009</v>
+        <v>63.03031838366022</v>
       </c>
       <c r="E97">
-        <v>55.79000000000001</v>
+        <v>57.03200000000001</v>
       </c>
       <c r="F97">
-        <v>117.99</v>
+        <v>119.232</v>
       </c>
       <c r="G97">
         <v>0.198</v>
@@ -9223,37 +9223,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M97">
-        <v>27.822042</v>
+        <v>28.1149056</v>
       </c>
       <c r="N97">
-        <v>-18.372042</v>
+        <v>-18.6649056</v>
       </c>
       <c r="O97">
-        <v>-3.490687980000001</v>
+        <v>-3.546332064000001</v>
       </c>
       <c r="P97">
-        <v>-14.88135402</v>
+        <v>-15.118573536</v>
       </c>
       <c r="Q97">
-        <v>5.418645979999997</v>
+        <v>5.181426463999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5418271460664783</v>
+        <v>0.6658339325830981</v>
       </c>
       <c r="T97">
-        <v>8.363730285997457</v>
+        <v>10.45466285749683</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06453516244422317</v>
+        <v>0.06386292116876252</v>
       </c>
       <c r="W97">
-        <v>0.2205826086956522</v>
+        <v>0.2207411231884058</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3396587497064377</v>
+        <v>0.336120637730329</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2385448355641935</v>
+        <v>0.2404448355641934</v>
       </c>
       <c r="C98">
-        <v>-56.00368161633978</v>
+        <v>-57.60376161856603</v>
       </c>
       <c r="D98">
-        <v>63.03031838366022</v>
+        <v>62.67223838143397</v>
       </c>
       <c r="E98">
-        <v>57.032</v>
+        <v>58.274</v>
       </c>
       <c r="F98">
-        <v>119.232</v>
+        <v>120.474</v>
       </c>
       <c r="G98">
         <v>0.198</v>
@@ -9305,37 +9305,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M98">
-        <v>28.1149056</v>
+        <v>28.4077692</v>
       </c>
       <c r="N98">
-        <v>-18.6649056</v>
+        <v>-18.9577692</v>
       </c>
       <c r="O98">
-        <v>-3.546332064</v>
+        <v>-3.601976148</v>
       </c>
       <c r="P98">
-        <v>-15.118573536</v>
+        <v>-15.355793052</v>
       </c>
       <c r="Q98">
-        <v>5.181426463999999</v>
+        <v>4.944206948</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6658339325830964</v>
+        <v>0.8725119101107952</v>
       </c>
       <c r="T98">
-        <v>10.4546628574968</v>
+        <v>13.9395504766624</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06386292116876252</v>
+        <v>0.06320454053815672</v>
       </c>
       <c r="W98">
-        <v>0.2207411231884058</v>
+        <v>0.2208963693411027</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3361206377303291</v>
+        <v>0.3326554765166143</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2404448355641934</v>
+        <v>0.2423448355641935</v>
       </c>
       <c r="C99">
-        <v>-57.60376161856603</v>
+        <v>-59.19979604490587</v>
       </c>
       <c r="D99">
-        <v>62.67223838143397</v>
+        <v>62.31820395509413</v>
       </c>
       <c r="E99">
-        <v>58.274</v>
+        <v>59.51599999999999</v>
       </c>
       <c r="F99">
-        <v>120.474</v>
+        <v>121.716</v>
       </c>
       <c r="G99">
         <v>0.198</v>
@@ -9387,37 +9387,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M99">
-        <v>28.4077692</v>
+        <v>28.7006328</v>
       </c>
       <c r="N99">
-        <v>-18.9577692</v>
+        <v>-19.2506328</v>
       </c>
       <c r="O99">
-        <v>-3.601976148</v>
+        <v>-3.657620232</v>
       </c>
       <c r="P99">
-        <v>-15.355793052</v>
+        <v>-15.593012568</v>
       </c>
       <c r="Q99">
-        <v>4.944206948</v>
+        <v>4.706987431999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8725119101107952</v>
+        <v>1.285867865166193</v>
       </c>
       <c r="T99">
-        <v>13.9395504766624</v>
+        <v>20.9093257149936</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06320454053815672</v>
+        <v>0.06255959624695104</v>
       </c>
       <c r="W99">
-        <v>0.2208963693411027</v>
+        <v>0.2210484472049689</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3326554765166143</v>
+        <v>0.3292610328786897</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2423448355641935</v>
+        <v>0.2442448355641935</v>
       </c>
       <c r="C100">
-        <v>-59.19979604490587</v>
+        <v>-60.7918530704111</v>
       </c>
       <c r="D100">
-        <v>62.31820395509413</v>
+        <v>61.9681469295889</v>
       </c>
       <c r="E100">
-        <v>59.51599999999999</v>
+        <v>60.758</v>
       </c>
       <c r="F100">
-        <v>121.716</v>
+        <v>122.958</v>
       </c>
       <c r="G100">
         <v>0.198</v>
@@ -9469,37 +9469,37 @@
         <v>9.449999999999999</v>
       </c>
       <c r="M100">
-        <v>28.7006328</v>
+        <v>28.9934964</v>
       </c>
       <c r="N100">
-        <v>-19.2506328</v>
+        <v>-19.5434964</v>
       </c>
       <c r="O100">
-        <v>-3.657620232</v>
+        <v>-3.713264316000001</v>
       </c>
       <c r="P100">
-        <v>-15.593012568</v>
+        <v>-15.830232084</v>
       </c>
       <c r="Q100">
-        <v>4.706987431999998</v>
+        <v>4.469767915999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.285867865166193</v>
+        <v>2.525935730332386</v>
       </c>
       <c r="T100">
-        <v>20.9093257149936</v>
+        <v>41.81865142998719</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06255959624695104</v>
+        <v>0.06192768113334547</v>
       </c>
       <c r="W100">
-        <v>0.2210484472049689</v>
+        <v>0.2211974527887572</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3292610328786897</v>
+        <v>0.325935163859713</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2442448355641935</v>
-      </c>
-      <c r="C101">
-        <v>-60.7918530704111</v>
-      </c>
-      <c r="D101">
-        <v>61.9681469295889</v>
-      </c>
-      <c r="E101">
-        <v>60.758</v>
-      </c>
-      <c r="F101">
-        <v>122.958</v>
-      </c>
-      <c r="G101">
-        <v>0.198</v>
-      </c>
-      <c r="H101">
-        <v>62</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>29.75</v>
-      </c>
-      <c r="K101">
-        <v>20.3</v>
-      </c>
-      <c r="L101">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="M101">
-        <v>28.9934964</v>
-      </c>
-      <c r="N101">
-        <v>-19.5434964</v>
-      </c>
-      <c r="O101">
-        <v>-3.713264316000001</v>
-      </c>
-      <c r="P101">
-        <v>-15.830232084</v>
-      </c>
-      <c r="Q101">
-        <v>4.469767915999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.525935730332386</v>
-      </c>
-      <c r="T101">
-        <v>41.81865142998719</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06192768113334547</v>
-      </c>
-      <c r="W101">
-        <v>0.2211974527887572</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.325935163859713</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
